--- a/research/traditional_assets/database/data/belgium/belgium_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_farming_agriculture.xlsx
@@ -1385,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1522,22 +1522,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07600297733566436</v>
+        <v>0.07584671989232519</v>
       </c>
       <c r="C2">
-        <v>632.1685523747445</v>
+        <v>628.9534863415226</v>
       </c>
       <c r="D2">
-        <v>616.4685523747445</v>
+        <v>619.6744863415227</v>
       </c>
       <c r="E2">
-        <v>-30.6</v>
+        <v>-24.179</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.421</v>
       </c>
       <c r="G2">
         <v>15.7</v>
@@ -1558,28 +1558,28 @@
         <v>100.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3229763</v>
       </c>
       <c r="N2">
-        <v>100.2</v>
+        <v>99.87702370000001</v>
       </c>
       <c r="O2">
-        <v>25.05</v>
+        <v>24.969255925</v>
       </c>
       <c r="P2">
-        <v>75.15000000000001</v>
+        <v>74.90776777500001</v>
       </c>
       <c r="Q2">
-        <v>132.55</v>
+        <v>132.307767775</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07600297733566436</v>
+        <v>0.07623178777002546</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5931721862945856</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>310.2394819681816</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1604,22 +1604,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07584671989232519</v>
+        <v>0.07569046244898606</v>
       </c>
       <c r="C3">
-        <v>628.9534863415226</v>
+        <v>625.7719394313997</v>
       </c>
       <c r="D3">
-        <v>619.6744863415227</v>
+        <v>622.9139394313996</v>
       </c>
       <c r="E3">
-        <v>-24.179</v>
+        <v>-17.758</v>
       </c>
       <c r="F3">
-        <v>6.421</v>
+        <v>12.842</v>
       </c>
       <c r="G3">
         <v>15.7</v>
@@ -1640,28 +1640,28 @@
         <v>100.2</v>
       </c>
       <c r="M3">
-        <v>0.3229763</v>
+        <v>0.6459526</v>
       </c>
       <c r="N3">
-        <v>99.87702370000001</v>
+        <v>99.5540474</v>
       </c>
       <c r="O3">
-        <v>24.969255925</v>
+        <v>24.88851185</v>
       </c>
       <c r="P3">
-        <v>74.90776777500001</v>
+        <v>74.66553555</v>
       </c>
       <c r="Q3">
-        <v>132.307767775</v>
+        <v>132.06553555</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07623178777002546</v>
+        <v>0.07646526780508781</v>
       </c>
       <c r="T3">
-        <v>0.5931721862945856</v>
+        <v>0.5977231467541113</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>310.2394819681816</v>
+        <v>155.1197409840908</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1686,22 +1686,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07569046244898606</v>
+        <v>0.07553420500564688</v>
       </c>
       <c r="C4">
-        <v>625.7719394313997</v>
+        <v>622.6244400875429</v>
       </c>
       <c r="D4">
-        <v>622.9139394313996</v>
+        <v>626.1874400875429</v>
       </c>
       <c r="E4">
-        <v>-17.758</v>
+        <v>-11.337</v>
       </c>
       <c r="F4">
-        <v>12.842</v>
+        <v>19.263</v>
       </c>
       <c r="G4">
         <v>15.7</v>
@@ -1722,28 +1722,28 @@
         <v>100.2</v>
       </c>
       <c r="M4">
-        <v>0.6459526</v>
+        <v>0.9689289</v>
       </c>
       <c r="N4">
-        <v>99.5540474</v>
+        <v>99.23107110000001</v>
       </c>
       <c r="O4">
-        <v>24.88851185</v>
+        <v>24.807767775</v>
       </c>
       <c r="P4">
-        <v>74.66553555</v>
+        <v>74.42330332500001</v>
       </c>
       <c r="Q4">
-        <v>132.06553555</v>
+        <v>131.823303325</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07646526780508781</v>
+        <v>0.07670356186149163</v>
       </c>
       <c r="T4">
-        <v>0.5977231467541113</v>
+        <v>0.6023679414499159</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>155.1197409840908</v>
+        <v>103.4131606560605</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1768,22 +1768,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07553420500564688</v>
+        <v>0.07537794756230771</v>
       </c>
       <c r="C5">
-        <v>622.6244400875429</v>
+        <v>619.5115279199747</v>
       </c>
       <c r="D5">
-        <v>626.1874400875429</v>
+        <v>629.4955279199746</v>
       </c>
       <c r="E5">
-        <v>-11.337</v>
+        <v>-4.916</v>
       </c>
       <c r="F5">
-        <v>19.263</v>
+        <v>25.684</v>
       </c>
       <c r="G5">
         <v>15.7</v>
@@ -1804,28 +1804,28 @@
         <v>100.2</v>
       </c>
       <c r="M5">
-        <v>0.9689289</v>
+        <v>1.2919052</v>
       </c>
       <c r="N5">
-        <v>99.23107110000001</v>
+        <v>98.9080948</v>
       </c>
       <c r="O5">
-        <v>24.807767775</v>
+        <v>24.7270237</v>
       </c>
       <c r="P5">
-        <v>74.42330332500001</v>
+        <v>74.1810711</v>
       </c>
       <c r="Q5">
-        <v>131.823303325</v>
+        <v>131.5810711</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07670356186149163</v>
+        <v>0.07694682037740387</v>
       </c>
       <c r="T5">
-        <v>0.6023679414499159</v>
+        <v>0.6071095027018831</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>103.4131606560605</v>
+        <v>77.55987049204539</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1850,22 +1850,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07537794756230771</v>
+        <v>0.07522169011896856</v>
       </c>
       <c r="C6">
-        <v>619.5115279199747</v>
+        <v>616.4337540021088</v>
       </c>
       <c r="D6">
-        <v>629.4955279199746</v>
+        <v>632.8387540021088</v>
       </c>
       <c r="E6">
-        <v>-4.916</v>
+        <v>1.505000000000003</v>
       </c>
       <c r="F6">
-        <v>25.684</v>
+        <v>32.105</v>
       </c>
       <c r="G6">
         <v>15.7</v>
@@ -1886,28 +1886,28 @@
         <v>100.2</v>
       </c>
       <c r="M6">
-        <v>1.2919052</v>
+        <v>1.6148815</v>
       </c>
       <c r="N6">
-        <v>98.9080948</v>
+        <v>98.58511850000001</v>
       </c>
       <c r="O6">
-        <v>24.7270237</v>
+        <v>24.646279625</v>
       </c>
       <c r="P6">
-        <v>74.1810711</v>
+        <v>73.938838875</v>
       </c>
       <c r="Q6">
-        <v>131.5810711</v>
+        <v>131.338838875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07694682037740387</v>
+        <v>0.07719520012523007</v>
       </c>
       <c r="T6">
-        <v>0.6071095027018831</v>
+        <v>0.611950886295997</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>77.55987049204539</v>
+        <v>62.04789639363631</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1932,22 +1932,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07522169011896856</v>
+        <v>0.0750654326756294</v>
       </c>
       <c r="C7">
-        <v>616.4337540021088</v>
+        <v>613.3916811767841</v>
       </c>
       <c r="D7">
-        <v>632.8387540021088</v>
+        <v>636.217681176784</v>
       </c>
       <c r="E7">
-        <v>1.505000000000003</v>
+        <v>7.926000000000002</v>
       </c>
       <c r="F7">
-        <v>32.105</v>
+        <v>38.526</v>
       </c>
       <c r="G7">
         <v>15.7</v>
@@ -1968,28 +1968,28 @@
         <v>100.2</v>
       </c>
       <c r="M7">
-        <v>1.6148815</v>
+        <v>1.9378578</v>
       </c>
       <c r="N7">
-        <v>98.58511850000001</v>
+        <v>98.2621422</v>
       </c>
       <c r="O7">
-        <v>24.646279625</v>
+        <v>24.56553555</v>
       </c>
       <c r="P7">
-        <v>73.938838875</v>
+        <v>73.69660665000001</v>
       </c>
       <c r="Q7">
-        <v>131.338838875</v>
+        <v>131.09660665</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07719520012523007</v>
+        <v>0.07744886454854191</v>
       </c>
       <c r="T7">
-        <v>0.611950886295997</v>
+        <v>0.6168952780516879</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>62.04789639363631</v>
+        <v>51.70658032803026</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2014,22 +2014,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0750654326756294</v>
+        <v>0.07490917523229024</v>
       </c>
       <c r="C8">
-        <v>613.3916811767841</v>
+        <v>610.3858843721524</v>
       </c>
       <c r="D8">
-        <v>636.217681176784</v>
+        <v>639.6328843721524</v>
       </c>
       <c r="E8">
-        <v>7.926000000000002</v>
+        <v>14.34699999999999</v>
       </c>
       <c r="F8">
-        <v>38.526</v>
+        <v>44.947</v>
       </c>
       <c r="G8">
         <v>15.7</v>
@@ -2050,28 +2050,28 @@
         <v>100.2</v>
       </c>
       <c r="M8">
-        <v>1.9378578</v>
+        <v>2.2608341</v>
       </c>
       <c r="N8">
-        <v>98.2621422</v>
+        <v>97.93916590000001</v>
       </c>
       <c r="O8">
-        <v>24.56553555</v>
+        <v>24.484791475</v>
       </c>
       <c r="P8">
-        <v>73.69660665000001</v>
+        <v>73.454374425</v>
       </c>
       <c r="Q8">
-        <v>131.09660665</v>
+        <v>130.854374425</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07744886454854191</v>
+        <v>0.07770798412074219</v>
       </c>
       <c r="T8">
-        <v>0.6168952780516879</v>
+        <v>0.6219460008128773</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>51.70658032803026</v>
+        <v>44.31992599545452</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2096,22 +2096,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07490917523229022</v>
+        <v>0.07475291778895107</v>
       </c>
       <c r="C9">
-        <v>610.3858843721526</v>
+        <v>607.4169509277997</v>
       </c>
       <c r="D9">
-        <v>639.6328843721526</v>
+        <v>643.0849509277997</v>
       </c>
       <c r="E9">
-        <v>14.347</v>
+        <v>20.768</v>
       </c>
       <c r="F9">
-        <v>44.947</v>
+        <v>51.368</v>
       </c>
       <c r="G9">
         <v>15.7</v>
@@ -2132,28 +2132,28 @@
         <v>100.2</v>
       </c>
       <c r="M9">
-        <v>2.2608341</v>
+        <v>2.5838104</v>
       </c>
       <c r="N9">
-        <v>97.93916590000001</v>
+        <v>97.6161896</v>
       </c>
       <c r="O9">
-        <v>24.484791475</v>
+        <v>24.4040474</v>
       </c>
       <c r="P9">
-        <v>73.454374425</v>
+        <v>73.2121422</v>
       </c>
       <c r="Q9">
-        <v>130.854374425</v>
+        <v>130.6121422</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07770798412074219</v>
+        <v>0.07797273672712074</v>
       </c>
       <c r="T9">
-        <v>0.6219460008128773</v>
+        <v>0.6271065218949624</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.31992599545452</v>
+        <v>38.7799352460227</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2178,22 +2178,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07475291778895107</v>
+        <v>0.07459666034561192</v>
       </c>
       <c r="C10">
-        <v>607.4169509277997</v>
+        <v>604.4854809314821</v>
       </c>
       <c r="D10">
-        <v>643.0849509277997</v>
+        <v>646.5744809314821</v>
       </c>
       <c r="E10">
-        <v>20.768</v>
+        <v>27.189</v>
       </c>
       <c r="F10">
-        <v>51.368</v>
+        <v>57.789</v>
       </c>
       <c r="G10">
         <v>15.7</v>
@@ -2214,28 +2214,28 @@
         <v>100.2</v>
       </c>
       <c r="M10">
-        <v>2.5838104</v>
+        <v>2.9067867</v>
       </c>
       <c r="N10">
-        <v>97.6161896</v>
+        <v>97.29321330000001</v>
       </c>
       <c r="O10">
-        <v>24.4040474</v>
+        <v>24.323303325</v>
       </c>
       <c r="P10">
-        <v>73.2121422</v>
+        <v>72.96990997500001</v>
       </c>
       <c r="Q10">
-        <v>130.6121422</v>
+        <v>130.369909975</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07797273672712074</v>
+        <v>0.078243308072101</v>
       </c>
       <c r="T10">
-        <v>0.6271065218949624</v>
+        <v>0.6323804610228073</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.7799352460227</v>
+        <v>34.47105355202017</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2260,22 +2260,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07459666034561192</v>
+        <v>0.07444040290227275</v>
       </c>
       <c r="C11">
-        <v>604.4854809314821</v>
+        <v>601.5920875668864</v>
       </c>
       <c r="D11">
-        <v>646.5744809314821</v>
+        <v>650.1020875668864</v>
       </c>
       <c r="E11">
-        <v>27.189</v>
+        <v>33.60999999999999</v>
       </c>
       <c r="F11">
-        <v>57.789</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="G11">
         <v>15.7</v>
@@ -2296,28 +2296,28 @@
         <v>100.2</v>
       </c>
       <c r="M11">
-        <v>2.9067867</v>
+        <v>3.229763</v>
       </c>
       <c r="N11">
-        <v>97.29321330000001</v>
+        <v>96.970237</v>
       </c>
       <c r="O11">
-        <v>24.323303325</v>
+        <v>24.24255925</v>
       </c>
       <c r="P11">
-        <v>72.96990997500001</v>
+        <v>72.72767775</v>
       </c>
       <c r="Q11">
-        <v>130.369909975</v>
+        <v>130.12767775</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.078243308072101</v>
+        <v>0.07851989211363639</v>
       </c>
       <c r="T11">
-        <v>0.6323804610228073</v>
+        <v>0.6377715987979379</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.47105355202017</v>
+        <v>31.02394819681816</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2342,22 +2342,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07444040290227275</v>
+        <v>0.07428414545893358</v>
       </c>
       <c r="C12">
-        <v>601.5920875668864</v>
+        <v>598.7373974728343</v>
       </c>
       <c r="D12">
-        <v>650.1020875668864</v>
+        <v>653.6683974728343</v>
       </c>
       <c r="E12">
-        <v>33.61000000000001</v>
+        <v>40.031</v>
       </c>
       <c r="F12">
-        <v>64.21000000000001</v>
+        <v>70.631</v>
       </c>
       <c r="G12">
         <v>15.7</v>
@@ -2378,28 +2378,28 @@
         <v>100.2</v>
       </c>
       <c r="M12">
-        <v>3.229763</v>
+        <v>3.5527393</v>
       </c>
       <c r="N12">
-        <v>96.970237</v>
+        <v>96.6472607</v>
       </c>
       <c r="O12">
-        <v>24.24255925</v>
+        <v>24.161815175</v>
       </c>
       <c r="P12">
-        <v>72.72767775</v>
+        <v>72.485445525</v>
       </c>
       <c r="Q12">
-        <v>130.12767775</v>
+        <v>129.885445525</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07851989211363639</v>
+        <v>0.07880269152689168</v>
       </c>
       <c r="T12">
-        <v>0.6377715987979379</v>
+        <v>0.6432838857365545</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.02394819681815</v>
+        <v>28.20358926983469</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2424,22 +2424,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07428414545893358</v>
+        <v>0.07412788801559443</v>
       </c>
       <c r="C13">
-        <v>598.7373974728343</v>
+        <v>595.9220511143792</v>
       </c>
       <c r="D13">
-        <v>653.6683974728343</v>
+        <v>657.2740511143792</v>
       </c>
       <c r="E13">
-        <v>40.031</v>
+        <v>46.45200000000001</v>
       </c>
       <c r="F13">
-        <v>70.631</v>
+        <v>77.05200000000001</v>
       </c>
       <c r="G13">
         <v>15.7</v>
@@ -2460,28 +2460,28 @@
         <v>100.2</v>
       </c>
       <c r="M13">
-        <v>3.5527393</v>
+        <v>3.8757156</v>
       </c>
       <c r="N13">
-        <v>96.6472607</v>
+        <v>96.3242844</v>
       </c>
       <c r="O13">
-        <v>24.161815175</v>
+        <v>24.0810711</v>
       </c>
       <c r="P13">
-        <v>72.485445525</v>
+        <v>72.24321329999999</v>
       </c>
       <c r="Q13">
-        <v>129.885445525</v>
+        <v>129.6432133</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07880269152689168</v>
+        <v>0.07909191819953912</v>
       </c>
       <c r="T13">
-        <v>0.6432838857365545</v>
+        <v>0.6489214519237759</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.20358926983469</v>
+        <v>25.85329016401513</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2506,22 +2506,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07412788801559443</v>
+        <v>0.07397163057225528</v>
       </c>
       <c r="C14">
-        <v>595.9220511143792</v>
+        <v>593.1467031662504</v>
       </c>
       <c r="D14">
-        <v>657.2740511143792</v>
+        <v>660.9197031662503</v>
       </c>
       <c r="E14">
-        <v>46.45200000000001</v>
+        <v>52.873</v>
       </c>
       <c r="F14">
-        <v>77.05200000000001</v>
+        <v>83.473</v>
       </c>
       <c r="G14">
         <v>15.7</v>
@@ -2542,28 +2542,28 @@
         <v>100.2</v>
       </c>
       <c r="M14">
-        <v>3.8757156</v>
+        <v>4.1986919</v>
       </c>
       <c r="N14">
-        <v>96.3242844</v>
+        <v>96.0013081</v>
       </c>
       <c r="O14">
-        <v>24.0810711</v>
+        <v>24.000327025</v>
       </c>
       <c r="P14">
-        <v>72.24321329999999</v>
+        <v>72.000981075</v>
       </c>
       <c r="Q14">
-        <v>129.6432133</v>
+        <v>129.400981075</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07909191819953912</v>
+        <v>0.07938779376121297</v>
       </c>
       <c r="T14">
-        <v>0.6489214519237759</v>
+        <v>0.6546886173336922</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.85329016401513</v>
+        <v>23.86457553601397</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2588,22 +2588,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07397163057225528</v>
+        <v>0.0738153731289161</v>
       </c>
       <c r="C15">
-        <v>593.1467031662504</v>
+        <v>590.4120229091294</v>
       </c>
       <c r="D15">
-        <v>660.9197031662503</v>
+        <v>664.6060229091294</v>
       </c>
       <c r="E15">
-        <v>52.873</v>
+        <v>59.294</v>
       </c>
       <c r="F15">
-        <v>83.473</v>
+        <v>89.89400000000001</v>
       </c>
       <c r="G15">
         <v>15.7</v>
@@ -2624,28 +2624,28 @@
         <v>100.2</v>
       </c>
       <c r="M15">
-        <v>4.1986919</v>
+        <v>4.5216682</v>
       </c>
       <c r="N15">
-        <v>96.0013081</v>
+        <v>95.67833180000001</v>
       </c>
       <c r="O15">
-        <v>24.000327025</v>
+        <v>23.91958295</v>
       </c>
       <c r="P15">
-        <v>72.000981075</v>
+        <v>71.75874885</v>
       </c>
       <c r="Q15">
-        <v>129.400981075</v>
+        <v>129.15874885</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07938779376121297</v>
+        <v>0.07969055014990245</v>
       </c>
       <c r="T15">
-        <v>0.6546886173336922</v>
+        <v>0.6605899028694204</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.86457553601397</v>
+        <v>22.15996299772726</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2670,22 +2670,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0738153731289161</v>
+        <v>0.07365911568557694</v>
       </c>
       <c r="C16">
-        <v>590.4120229091294</v>
+        <v>587.718694639261</v>
       </c>
       <c r="D16">
-        <v>664.6060229091294</v>
+        <v>668.333694639261</v>
       </c>
       <c r="E16">
-        <v>59.294</v>
+        <v>65.715</v>
       </c>
       <c r="F16">
-        <v>89.89400000000001</v>
+        <v>96.31500000000001</v>
       </c>
       <c r="G16">
         <v>15.7</v>
@@ -2706,28 +2706,28 @@
         <v>100.2</v>
       </c>
       <c r="M16">
-        <v>4.5216682</v>
+        <v>4.8446445</v>
       </c>
       <c r="N16">
-        <v>95.67833180000001</v>
+        <v>95.3553555</v>
       </c>
       <c r="O16">
-        <v>23.91958295</v>
+        <v>23.838838875</v>
       </c>
       <c r="P16">
-        <v>71.75874885</v>
+        <v>71.51651662500001</v>
       </c>
       <c r="Q16">
-        <v>129.15874885</v>
+        <v>128.916516625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07969055014990245</v>
+        <v>0.08000043021832581</v>
       </c>
       <c r="T16">
-        <v>0.6605899028694204</v>
+        <v>0.6666300421824599</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.15996299772726</v>
+        <v>20.6826321312121</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2752,22 +2752,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07365911568557694</v>
+        <v>0.07350285824223779</v>
       </c>
       <c r="C17">
-        <v>587.718694639261</v>
+        <v>585.0674180919304</v>
       </c>
       <c r="D17">
-        <v>668.333694639261</v>
+        <v>672.1034180919304</v>
       </c>
       <c r="E17">
-        <v>65.715</v>
+        <v>72.136</v>
       </c>
       <c r="F17">
-        <v>96.315</v>
+        <v>102.736</v>
       </c>
       <c r="G17">
         <v>15.7</v>
@@ -2788,28 +2788,28 @@
         <v>100.2</v>
       </c>
       <c r="M17">
-        <v>4.844644499999999</v>
+        <v>5.1676208</v>
       </c>
       <c r="N17">
-        <v>95.3553555</v>
+        <v>95.03237920000001</v>
       </c>
       <c r="O17">
-        <v>23.838838875</v>
+        <v>23.7580948</v>
       </c>
       <c r="P17">
-        <v>71.51651662500001</v>
+        <v>71.2742844</v>
       </c>
       <c r="Q17">
-        <v>128.916516625</v>
+        <v>128.6742844</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08000043021832581</v>
+        <v>0.08031768838361641</v>
       </c>
       <c r="T17">
-        <v>0.6666300421824599</v>
+        <v>0.6728139943362861</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.68263213121211</v>
+        <v>19.38996762301135</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2834,22 +2834,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07350285824223779</v>
+        <v>0.07334660079889863</v>
       </c>
       <c r="C18">
-        <v>585.0674180919304</v>
+        <v>582.458908879351</v>
       </c>
       <c r="D18">
-        <v>672.1034180919304</v>
+        <v>675.915908879351</v>
       </c>
       <c r="E18">
-        <v>72.136</v>
+        <v>78.55700000000002</v>
       </c>
       <c r="F18">
-        <v>102.736</v>
+        <v>109.157</v>
       </c>
       <c r="G18">
         <v>15.7</v>
@@ -2870,28 +2870,28 @@
         <v>100.2</v>
       </c>
       <c r="M18">
-        <v>5.1676208</v>
+        <v>5.4905971</v>
       </c>
       <c r="N18">
-        <v>95.03237920000001</v>
+        <v>94.7094029</v>
       </c>
       <c r="O18">
-        <v>23.7580948</v>
+        <v>23.677350725</v>
       </c>
       <c r="P18">
-        <v>71.2742844</v>
+        <v>71.032052175</v>
       </c>
       <c r="Q18">
-        <v>128.6742844</v>
+        <v>128.432052175</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08031768838361641</v>
+        <v>0.08064259132397425</v>
       </c>
       <c r="T18">
-        <v>0.6728139943362861</v>
+        <v>0.6791469573853852</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.38996762301135</v>
+        <v>18.24938129224597</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2916,22 +2916,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07334660079889863</v>
+        <v>0.07319034335555946</v>
       </c>
       <c r="C19">
-        <v>582.458908879351</v>
+        <v>579.89389894354</v>
       </c>
       <c r="D19">
-        <v>675.915908879351</v>
+        <v>679.7718989435399</v>
       </c>
       <c r="E19">
-        <v>78.55700000000002</v>
+        <v>84.97800000000001</v>
       </c>
       <c r="F19">
-        <v>109.157</v>
+        <v>115.578</v>
       </c>
       <c r="G19">
         <v>15.7</v>
@@ -2952,28 +2952,28 @@
         <v>100.2</v>
       </c>
       <c r="M19">
-        <v>5.4905971</v>
+        <v>5.813573400000001</v>
       </c>
       <c r="N19">
-        <v>94.7094029</v>
+        <v>94.38642660000001</v>
       </c>
       <c r="O19">
-        <v>23.677350725</v>
+        <v>23.59660665</v>
       </c>
       <c r="P19">
-        <v>71.032052175</v>
+        <v>70.78981995000001</v>
       </c>
       <c r="Q19">
-        <v>128.432052175</v>
+        <v>128.18981995</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08064259132397425</v>
+        <v>0.08097541872629203</v>
       </c>
       <c r="T19">
-        <v>0.6791469573853852</v>
+        <v>0.6856343829478769</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.24938129224597</v>
+        <v>17.23552677601009</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2998,22 +2998,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07319034335555948</v>
+        <v>0.07303408591222031</v>
       </c>
       <c r="C20">
-        <v>579.8938989435395</v>
+        <v>577.373137024784</v>
       </c>
       <c r="D20">
-        <v>679.7718989435394</v>
+        <v>683.672137024784</v>
       </c>
       <c r="E20">
-        <v>84.97800000000001</v>
+        <v>91.399</v>
       </c>
       <c r="F20">
-        <v>115.578</v>
+        <v>121.999</v>
       </c>
       <c r="G20">
         <v>15.7</v>
@@ -3034,28 +3034,28 @@
         <v>100.2</v>
       </c>
       <c r="M20">
-        <v>5.8135734</v>
+        <v>6.1365497</v>
       </c>
       <c r="N20">
-        <v>94.38642660000001</v>
+        <v>94.0634503</v>
       </c>
       <c r="O20">
-        <v>23.59660665</v>
+        <v>23.515862575</v>
       </c>
       <c r="P20">
-        <v>70.78981995000001</v>
+        <v>70.547587725</v>
       </c>
       <c r="Q20">
-        <v>128.18981995</v>
+        <v>127.947587725</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08097541872629203</v>
+        <v>0.08131646408916088</v>
       </c>
       <c r="T20">
-        <v>0.6856343829478769</v>
+        <v>0.6922819918575908</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.23552677601009</v>
+        <v>16.32839378779903</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3080,22 +3080,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07303408591222031</v>
+        <v>0.07287782846888115</v>
       </c>
       <c r="C21">
-        <v>577.373137024784</v>
+        <v>574.8973891463302</v>
       </c>
       <c r="D21">
-        <v>683.672137024784</v>
+        <v>687.6173891463301</v>
       </c>
       <c r="E21">
-        <v>91.399</v>
+        <v>97.82000000000002</v>
       </c>
       <c r="F21">
-        <v>121.999</v>
+        <v>128.42</v>
       </c>
       <c r="G21">
         <v>15.7</v>
@@ -3116,28 +3116,28 @@
         <v>100.2</v>
       </c>
       <c r="M21">
-        <v>6.1365497</v>
+        <v>6.459526</v>
       </c>
       <c r="N21">
-        <v>94.0634503</v>
+        <v>93.74047400000001</v>
       </c>
       <c r="O21">
-        <v>23.515862575</v>
+        <v>23.4351185</v>
       </c>
       <c r="P21">
-        <v>70.547587725</v>
+        <v>70.3053555</v>
       </c>
       <c r="Q21">
-        <v>127.947587725</v>
+        <v>127.7053555</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08131646408916088</v>
+        <v>0.08166603558610143</v>
       </c>
       <c r="T21">
-        <v>0.6922819918575908</v>
+        <v>0.6990957909900473</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.32839378779903</v>
+        <v>15.51197409840908</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3162,22 +3162,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07287782846888115</v>
+        <v>0.072721571025542</v>
       </c>
       <c r="C22">
-        <v>574.8973891463302</v>
+        <v>572.4674391159476</v>
       </c>
       <c r="D22">
-        <v>687.6173891463301</v>
+        <v>691.6084391159476</v>
       </c>
       <c r="E22">
-        <v>97.82000000000002</v>
+        <v>104.241</v>
       </c>
       <c r="F22">
-        <v>128.42</v>
+        <v>134.841</v>
       </c>
       <c r="G22">
         <v>15.7</v>
@@ -3198,28 +3198,28 @@
         <v>100.2</v>
       </c>
       <c r="M22">
-        <v>6.459526</v>
+        <v>6.7825023</v>
       </c>
       <c r="N22">
-        <v>93.74047400000001</v>
+        <v>93.4174977</v>
       </c>
       <c r="O22">
-        <v>23.4351185</v>
+        <v>23.354374425</v>
       </c>
       <c r="P22">
-        <v>70.3053555</v>
+        <v>70.063123275</v>
       </c>
       <c r="Q22">
-        <v>127.7053555</v>
+        <v>127.463123275</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08166603558610143</v>
+        <v>0.08202445699435695</v>
       </c>
       <c r="T22">
-        <v>0.6990957909900473</v>
+        <v>0.7060820913663636</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.51197409840908</v>
+        <v>14.7733086651515</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3244,22 +3244,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.072721571025542</v>
+        <v>0.07256531358220283</v>
       </c>
       <c r="C23">
-        <v>572.4674391159476</v>
+        <v>570.0840890450675</v>
       </c>
       <c r="D23">
-        <v>691.6084391159476</v>
+        <v>695.6460890450674</v>
       </c>
       <c r="E23">
-        <v>104.241</v>
+        <v>110.662</v>
       </c>
       <c r="F23">
-        <v>134.841</v>
+        <v>141.262</v>
       </c>
       <c r="G23">
         <v>15.7</v>
@@ -3280,28 +3280,28 @@
         <v>100.2</v>
       </c>
       <c r="M23">
-        <v>6.7825023</v>
+        <v>7.1054786</v>
       </c>
       <c r="N23">
-        <v>93.4174977</v>
+        <v>93.0945214</v>
       </c>
       <c r="O23">
-        <v>23.354374425</v>
+        <v>23.27363035</v>
       </c>
       <c r="P23">
-        <v>70.063123275</v>
+        <v>69.82089105</v>
       </c>
       <c r="Q23">
-        <v>127.463123275</v>
+        <v>127.22089105</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08202445699435695</v>
+        <v>0.08239206869513183</v>
       </c>
       <c r="T23">
-        <v>0.7060820913663636</v>
+        <v>0.7132475276497648</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.7733086651515</v>
+        <v>14.10179463491735</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3326,22 +3326,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07256531358220283</v>
+        <v>0.07240905613886366</v>
       </c>
       <c r="C24">
-        <v>570.0840890450675</v>
+        <v>567.7481598862056</v>
       </c>
       <c r="D24">
-        <v>695.6460890450674</v>
+        <v>699.7311598862055</v>
       </c>
       <c r="E24">
-        <v>110.662</v>
+        <v>117.083</v>
       </c>
       <c r="F24">
-        <v>141.262</v>
+        <v>147.683</v>
       </c>
       <c r="G24">
         <v>15.7</v>
@@ -3362,28 +3362,28 @@
         <v>100.2</v>
       </c>
       <c r="M24">
-        <v>7.1054786</v>
+        <v>7.428454900000001</v>
       </c>
       <c r="N24">
-        <v>93.0945214</v>
+        <v>92.7715451</v>
       </c>
       <c r="O24">
-        <v>23.27363035</v>
+        <v>23.192886275</v>
       </c>
       <c r="P24">
-        <v>69.82089105</v>
+        <v>69.57865882499999</v>
       </c>
       <c r="Q24">
-        <v>127.22089105</v>
+        <v>126.978658825</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08239206869513183</v>
+        <v>0.08276922875177098</v>
       </c>
       <c r="T24">
-        <v>0.7132475276497648</v>
+        <v>0.7205990791613064</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.10179463491735</v>
+        <v>13.48867312905137</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3408,22 +3408,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07240905613886366</v>
+        <v>0.07225279869552451</v>
       </c>
       <c r="C25">
-        <v>567.7481598862056</v>
+        <v>565.460491989438</v>
       </c>
       <c r="D25">
-        <v>699.7311598862055</v>
+        <v>703.864491989438</v>
       </c>
       <c r="E25">
-        <v>117.083</v>
+        <v>123.504</v>
       </c>
       <c r="F25">
-        <v>147.683</v>
+        <v>154.104</v>
       </c>
       <c r="G25">
         <v>15.7</v>
@@ -3444,28 +3444,28 @@
         <v>100.2</v>
       </c>
       <c r="M25">
-        <v>7.428454900000001</v>
+        <v>7.7514312</v>
       </c>
       <c r="N25">
-        <v>92.7715451</v>
+        <v>92.4485688</v>
       </c>
       <c r="O25">
-        <v>23.192886275</v>
+        <v>23.1121422</v>
       </c>
       <c r="P25">
-        <v>69.57865882499999</v>
+        <v>69.33642660000001</v>
       </c>
       <c r="Q25">
-        <v>126.978658825</v>
+        <v>126.7364266</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08276922875177098</v>
+        <v>0.08315631407305857</v>
       </c>
       <c r="T25">
-        <v>0.7205990791613064</v>
+        <v>0.7281440925547308</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.48867312905137</v>
+        <v>12.92664508200757</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3490,22 +3490,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07225279869552451</v>
+        <v>0.07237779125218534</v>
       </c>
       <c r="C26">
-        <v>565.460491989438</v>
+        <v>555.7292913199484</v>
       </c>
       <c r="D26">
-        <v>703.864491989438</v>
+        <v>700.5542913199483</v>
       </c>
       <c r="E26">
-        <v>123.504</v>
+        <v>129.925</v>
       </c>
       <c r="F26">
-        <v>154.104</v>
+        <v>160.525</v>
       </c>
       <c r="G26">
         <v>15.7</v>
@@ -3526,45 +3526,45 @@
         <v>100.2</v>
       </c>
       <c r="M26">
-        <v>7.7514312</v>
+        <v>8.315194999999999</v>
       </c>
       <c r="N26">
-        <v>92.4485688</v>
+        <v>91.884805</v>
       </c>
       <c r="O26">
-        <v>23.1121422</v>
+        <v>22.97120125</v>
       </c>
       <c r="P26">
-        <v>69.33642660000001</v>
+        <v>68.91360374999999</v>
       </c>
       <c r="Q26">
-        <v>126.7364266</v>
+        <v>126.31360375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08315631407305857</v>
+        <v>0.08355372166958046</v>
       </c>
       <c r="T26">
-        <v>0.7281440925547308</v>
+        <v>0.7358903063053129</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>12.92664508200757</v>
+        <v>12.05022852741277</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3572,22 +3572,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07237779125218534</v>
+        <v>0.07223278380884618</v>
       </c>
       <c r="C27">
-        <v>555.7292913199484</v>
+        <v>553.1514577241841</v>
       </c>
       <c r="D27">
-        <v>700.5542913199483</v>
+        <v>704.3974577241841</v>
       </c>
       <c r="E27">
-        <v>129.925</v>
+        <v>136.346</v>
       </c>
       <c r="F27">
-        <v>160.525</v>
+        <v>166.946</v>
       </c>
       <c r="G27">
         <v>15.7</v>
@@ -3608,28 +3608,28 @@
         <v>100.2</v>
       </c>
       <c r="M27">
-        <v>8.315194999999999</v>
+        <v>8.647802799999999</v>
       </c>
       <c r="N27">
-        <v>91.884805</v>
+        <v>91.55219720000001</v>
       </c>
       <c r="O27">
-        <v>22.97120125</v>
+        <v>22.8880493</v>
       </c>
       <c r="P27">
-        <v>68.91360374999999</v>
+        <v>68.6641479</v>
       </c>
       <c r="Q27">
-        <v>126.31360375</v>
+        <v>126.0641479</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08355372166958046</v>
+        <v>0.08396187001195429</v>
       </c>
       <c r="T27">
-        <v>0.7358903063053129</v>
+        <v>0.7438458771842893</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.05022852741277</v>
+        <v>11.58675819943536</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3654,22 +3654,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07223278380884618</v>
+        <v>0.07208777636550703</v>
       </c>
       <c r="C28">
-        <v>553.1514577241841</v>
+        <v>550.6160231299064</v>
       </c>
       <c r="D28">
-        <v>704.3974577241841</v>
+        <v>708.2830231299064</v>
       </c>
       <c r="E28">
-        <v>136.346</v>
+        <v>142.767</v>
       </c>
       <c r="F28">
-        <v>166.946</v>
+        <v>173.367</v>
       </c>
       <c r="G28">
         <v>15.7</v>
@@ -3690,28 +3690,28 @@
         <v>100.2</v>
       </c>
       <c r="M28">
-        <v>8.647802799999999</v>
+        <v>8.980410600000001</v>
       </c>
       <c r="N28">
-        <v>91.55219720000001</v>
+        <v>91.2195894</v>
       </c>
       <c r="O28">
-        <v>22.8880493</v>
+        <v>22.80489735</v>
       </c>
       <c r="P28">
-        <v>68.6641479</v>
+        <v>68.41469205</v>
       </c>
       <c r="Q28">
-        <v>126.0641479</v>
+        <v>125.81469205</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08396187001195429</v>
+        <v>0.08438120050069456</v>
       </c>
       <c r="T28">
-        <v>0.7438458771842893</v>
+        <v>0.7520194089092651</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.58675819943536</v>
+        <v>11.15761900686367</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3736,22 +3736,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07208777636550703</v>
+        <v>0.07194276892216786</v>
       </c>
       <c r="C29">
-        <v>550.6160231299064</v>
+        <v>548.1236930672945</v>
       </c>
       <c r="D29">
-        <v>708.2830231299064</v>
+        <v>712.2116930672945</v>
       </c>
       <c r="E29">
-        <v>142.767</v>
+        <v>149.188</v>
       </c>
       <c r="F29">
-        <v>173.367</v>
+        <v>179.788</v>
       </c>
       <c r="G29">
         <v>15.7</v>
@@ -3772,28 +3772,28 @@
         <v>100.2</v>
       </c>
       <c r="M29">
-        <v>8.980410600000001</v>
+        <v>9.313018400000001</v>
       </c>
       <c r="N29">
-        <v>91.2195894</v>
+        <v>90.8869816</v>
       </c>
       <c r="O29">
-        <v>22.80489735</v>
+        <v>22.7217454</v>
       </c>
       <c r="P29">
-        <v>68.41469205</v>
+        <v>68.1652362</v>
       </c>
       <c r="Q29">
-        <v>125.81469205</v>
+        <v>125.5652362</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08438120050069456</v>
+        <v>0.08481217905856647</v>
       </c>
       <c r="T29">
-        <v>0.7520194089092651</v>
+        <v>0.7604199831821568</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.15761900686367</v>
+        <v>10.7591326137614</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3818,22 +3818,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07194276892216786</v>
+        <v>0.0717977614788287</v>
       </c>
       <c r="C30">
-        <v>548.1236930672945</v>
+        <v>545.6751888074392</v>
       </c>
       <c r="D30">
-        <v>712.2116930672945</v>
+        <v>716.1841888074392</v>
       </c>
       <c r="E30">
-        <v>149.188</v>
+        <v>155.609</v>
       </c>
       <c r="F30">
-        <v>179.788</v>
+        <v>186.209</v>
       </c>
       <c r="G30">
         <v>15.7</v>
@@ -3854,28 +3854,28 @@
         <v>100.2</v>
       </c>
       <c r="M30">
-        <v>9.313018400000001</v>
+        <v>9.645626200000001</v>
       </c>
       <c r="N30">
-        <v>90.8869816</v>
+        <v>90.55437380000001</v>
       </c>
       <c r="O30">
-        <v>22.7217454</v>
+        <v>22.63859345</v>
       </c>
       <c r="P30">
-        <v>68.1652362</v>
+        <v>67.91578035000001</v>
       </c>
       <c r="Q30">
-        <v>125.5652362</v>
+        <v>125.31578035</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08481217905856647</v>
+        <v>0.08525529785750521</v>
       </c>
       <c r="T30">
-        <v>0.7604199831821568</v>
+        <v>0.7690571933500594</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.7591326137614</v>
+        <v>10.38812804087308</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3900,22 +3900,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0717977614788287</v>
+        <v>0.07165275403548953</v>
       </c>
       <c r="C31">
-        <v>545.6751888074393</v>
+        <v>543.2712478037977</v>
       </c>
       <c r="D31">
-        <v>716.1841888074392</v>
+        <v>720.2012478037976</v>
       </c>
       <c r="E31">
-        <v>155.609</v>
+        <v>162.03</v>
       </c>
       <c r="F31">
-        <v>186.209</v>
+        <v>192.63</v>
       </c>
       <c r="G31">
         <v>15.7</v>
@@ -3936,28 +3936,28 @@
         <v>100.2</v>
       </c>
       <c r="M31">
-        <v>9.645626200000001</v>
+        <v>9.978233999999999</v>
       </c>
       <c r="N31">
-        <v>90.55437380000001</v>
+        <v>90.221766</v>
       </c>
       <c r="O31">
-        <v>22.63859345</v>
+        <v>22.5554415</v>
       </c>
       <c r="P31">
-        <v>67.91578035000001</v>
+        <v>67.6663245</v>
       </c>
       <c r="Q31">
-        <v>125.31578035</v>
+        <v>125.0663245</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08525529785750521</v>
+        <v>0.08571107719355647</v>
       </c>
       <c r="T31">
-        <v>0.7690571933500594</v>
+        <v>0.7779411809513308</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.38812804087308</v>
+        <v>10.04185710617731</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3982,22 +3982,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07165275403548953</v>
+        <v>0.07190299659215037</v>
       </c>
       <c r="C32">
-        <v>543.2712478037977</v>
+        <v>529.945868035578</v>
       </c>
       <c r="D32">
-        <v>720.2012478037976</v>
+        <v>713.296868035578</v>
       </c>
       <c r="E32">
-        <v>162.03</v>
+        <v>168.451</v>
       </c>
       <c r="F32">
-        <v>192.63</v>
+        <v>199.051</v>
       </c>
       <c r="G32">
         <v>15.7</v>
@@ -4018,45 +4018,45 @@
         <v>100.2</v>
       </c>
       <c r="M32">
-        <v>9.978233999999999</v>
+        <v>10.6492285</v>
       </c>
       <c r="N32">
-        <v>90.221766</v>
+        <v>89.5507715</v>
       </c>
       <c r="O32">
-        <v>22.5554415</v>
+        <v>22.387692875</v>
       </c>
       <c r="P32">
-        <v>67.6663245</v>
+        <v>67.163078625</v>
       </c>
       <c r="Q32">
-        <v>125.0663245</v>
+        <v>124.563078625</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08571107719355647</v>
+        <v>0.08618006752485562</v>
       </c>
       <c r="T32">
-        <v>0.7779411809513308</v>
+        <v>0.7870826754395955</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>10.04185710617731</v>
+        <v>9.409132314138999</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4064,22 +4064,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07190299659215037</v>
+        <v>0.0717707391488112</v>
       </c>
       <c r="C33">
-        <v>529.945868035578</v>
+        <v>527.1573722768961</v>
       </c>
       <c r="D33">
-        <v>713.296868035578</v>
+        <v>716.9293722768961</v>
       </c>
       <c r="E33">
-        <v>168.451</v>
+        <v>174.872</v>
       </c>
       <c r="F33">
-        <v>199.051</v>
+        <v>205.472</v>
       </c>
       <c r="G33">
         <v>15.7</v>
@@ -4100,28 +4100,28 @@
         <v>100.2</v>
       </c>
       <c r="M33">
-        <v>10.6492285</v>
+        <v>10.992752</v>
       </c>
       <c r="N33">
-        <v>89.5507715</v>
+        <v>89.20724800000001</v>
       </c>
       <c r="O33">
-        <v>22.387692875</v>
+        <v>22.301812</v>
       </c>
       <c r="P33">
-        <v>67.163078625</v>
+        <v>66.90543600000001</v>
       </c>
       <c r="Q33">
-        <v>124.563078625</v>
+        <v>124.305436</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08618006752485562</v>
+        <v>0.08666285168942825</v>
       </c>
       <c r="T33">
-        <v>0.7870826754395955</v>
+        <v>0.7964930374128093</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.409132314138999</v>
+        <v>9.115096929322158</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4146,22 +4146,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0717707391488112</v>
+        <v>0.07163848170547205</v>
       </c>
       <c r="C34">
-        <v>527.1573722768961</v>
+        <v>524.4060633567711</v>
       </c>
       <c r="D34">
-        <v>716.9293722768961</v>
+        <v>720.5990633567711</v>
       </c>
       <c r="E34">
-        <v>174.872</v>
+        <v>181.293</v>
       </c>
       <c r="F34">
-        <v>205.472</v>
+        <v>211.893</v>
       </c>
       <c r="G34">
         <v>15.7</v>
@@ -4182,28 +4182,28 @@
         <v>100.2</v>
       </c>
       <c r="M34">
-        <v>10.992752</v>
+        <v>11.3362755</v>
       </c>
       <c r="N34">
-        <v>89.20724800000001</v>
+        <v>88.8637245</v>
       </c>
       <c r="O34">
-        <v>22.301812</v>
+        <v>22.215931125</v>
       </c>
       <c r="P34">
-        <v>66.90543600000001</v>
+        <v>66.64779337500001</v>
       </c>
       <c r="Q34">
-        <v>124.305436</v>
+        <v>124.047793375</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08666285168942825</v>
+        <v>0.08716004732160008</v>
       </c>
       <c r="T34">
-        <v>0.7964930374128093</v>
+        <v>0.8061843057135817</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.115096929322158</v>
+        <v>8.838881870857849</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4228,22 +4228,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07163848170547205</v>
+        <v>0.07150622426213288</v>
       </c>
       <c r="C35">
-        <v>524.4060633567711</v>
+        <v>521.6925152493682</v>
       </c>
       <c r="D35">
-        <v>720.5990633567711</v>
+        <v>724.3065152493681</v>
       </c>
       <c r="E35">
-        <v>181.293</v>
+        <v>187.714</v>
       </c>
       <c r="F35">
-        <v>211.893</v>
+        <v>218.314</v>
       </c>
       <c r="G35">
         <v>15.7</v>
@@ -4264,28 +4264,28 @@
         <v>100.2</v>
       </c>
       <c r="M35">
-        <v>11.3362755</v>
+        <v>11.679799</v>
       </c>
       <c r="N35">
-        <v>88.8637245</v>
+        <v>88.520201</v>
       </c>
       <c r="O35">
-        <v>22.215931125</v>
+        <v>22.13005025</v>
       </c>
       <c r="P35">
-        <v>66.64779337500001</v>
+        <v>66.39015075</v>
       </c>
       <c r="Q35">
-        <v>124.047793375</v>
+        <v>123.79015075</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08716004732160008</v>
+        <v>0.08767230948808014</v>
       </c>
       <c r="T35">
-        <v>0.8061843057135817</v>
+        <v>0.8161692488113471</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.838881870857849</v>
+        <v>8.578914757009088</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4310,22 +4310,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07150622426213288</v>
+        <v>0.07137396681879372</v>
       </c>
       <c r="C36">
-        <v>521.6925152493682</v>
+        <v>519.01731380223</v>
       </c>
       <c r="D36">
-        <v>724.3065152493681</v>
+        <v>728.0523138022299</v>
       </c>
       <c r="E36">
-        <v>187.714</v>
+        <v>194.135</v>
       </c>
       <c r="F36">
-        <v>218.314</v>
+        <v>224.735</v>
       </c>
       <c r="G36">
         <v>15.7</v>
@@ -4346,28 +4346,28 @@
         <v>100.2</v>
       </c>
       <c r="M36">
-        <v>11.679799</v>
+        <v>12.0233225</v>
       </c>
       <c r="N36">
-        <v>88.520201</v>
+        <v>88.1766775</v>
       </c>
       <c r="O36">
-        <v>22.13005025</v>
+        <v>22.044169375</v>
       </c>
       <c r="P36">
-        <v>66.39015075</v>
+        <v>66.132508125</v>
       </c>
       <c r="Q36">
-        <v>123.79015075</v>
+        <v>123.532508125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08767230948808014</v>
+        <v>0.08820033356737497</v>
       </c>
       <c r="T36">
-        <v>0.8161692488113471</v>
+        <v>0.8264614209275054</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.578914757009088</v>
+        <v>8.333802906808828</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4392,22 +4392,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07137396681879372</v>
+        <v>0.07124170937545457</v>
       </c>
       <c r="C37">
-        <v>519.01731380223</v>
+        <v>516.3810570448965</v>
       </c>
       <c r="D37">
-        <v>728.0523138022299</v>
+        <v>731.8370570448965</v>
       </c>
       <c r="E37">
-        <v>194.135</v>
+        <v>200.556</v>
       </c>
       <c r="F37">
-        <v>224.735</v>
+        <v>231.156</v>
       </c>
       <c r="G37">
         <v>15.7</v>
@@ -4428,28 +4428,28 @@
         <v>100.2</v>
       </c>
       <c r="M37">
-        <v>12.0233225</v>
+        <v>12.366846</v>
       </c>
       <c r="N37">
-        <v>88.1766775</v>
+        <v>87.83315400000001</v>
       </c>
       <c r="O37">
-        <v>22.044169375</v>
+        <v>21.9582885</v>
       </c>
       <c r="P37">
-        <v>66.132508125</v>
+        <v>65.8748655</v>
       </c>
       <c r="Q37">
-        <v>123.532508125</v>
+        <v>123.2748655</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08820033356737497</v>
+        <v>0.08874485839914777</v>
       </c>
       <c r="T37">
-        <v>0.8264614209275054</v>
+        <v>0.8370752234222935</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.333802906808828</v>
+        <v>8.102308381619693</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4474,22 +4474,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07124170937545457</v>
+        <v>0.07110945193211542</v>
       </c>
       <c r="C38">
-        <v>516.3810570448966</v>
+        <v>513.784355507195</v>
       </c>
       <c r="D38">
-        <v>731.8370570448965</v>
+        <v>735.6613555071949</v>
       </c>
       <c r="E38">
-        <v>200.556</v>
+        <v>206.977</v>
       </c>
       <c r="F38">
-        <v>231.156</v>
+        <v>237.577</v>
       </c>
       <c r="G38">
         <v>15.7</v>
@@ -4510,28 +4510,28 @@
         <v>100.2</v>
       </c>
       <c r="M38">
-        <v>12.366846</v>
+        <v>12.7103695</v>
       </c>
       <c r="N38">
-        <v>87.83315400000001</v>
+        <v>87.4896305</v>
       </c>
       <c r="O38">
-        <v>21.9582885</v>
+        <v>21.872407625</v>
       </c>
       <c r="P38">
-        <v>65.8748655</v>
+        <v>65.61722287500001</v>
       </c>
       <c r="Q38">
-        <v>123.2748655</v>
+        <v>123.017222875</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08874485839914777</v>
+        <v>0.08930666973351653</v>
       </c>
       <c r="T38">
-        <v>0.8370752234222935</v>
+        <v>0.8480259720280273</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.102308381619697</v>
+        <v>7.883327074008353</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4556,22 +4556,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07110945193211542</v>
+        <v>0.07097719448877625</v>
       </c>
       <c r="C39">
-        <v>513.784355507195</v>
+        <v>511.2278325475651</v>
       </c>
       <c r="D39">
-        <v>735.6613555071949</v>
+        <v>739.5258325475651</v>
       </c>
       <c r="E39">
-        <v>206.977</v>
+        <v>213.398</v>
       </c>
       <c r="F39">
-        <v>237.577</v>
+        <v>243.998</v>
       </c>
       <c r="G39">
         <v>15.7</v>
@@ -4592,28 +4592,28 @@
         <v>100.2</v>
       </c>
       <c r="M39">
-        <v>12.7103695</v>
+        <v>13.053893</v>
       </c>
       <c r="N39">
-        <v>87.4896305</v>
+        <v>87.146107</v>
       </c>
       <c r="O39">
-        <v>21.872407625</v>
+        <v>21.78652675</v>
       </c>
       <c r="P39">
-        <v>65.61722287500001</v>
+        <v>65.35958024999999</v>
       </c>
       <c r="Q39">
-        <v>123.017222875</v>
+        <v>122.75958025</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08930666973351653</v>
+        <v>0.08988660401415524</v>
       </c>
       <c r="T39">
-        <v>0.8480259720280273</v>
+        <v>0.8593299705887848</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.883327074008353</v>
+        <v>7.675871098376553</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4638,22 +4638,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07097719448877625</v>
+        <v>0.07107893704543709</v>
       </c>
       <c r="C40">
-        <v>511.2278325475651</v>
+        <v>501.8303921701519</v>
       </c>
       <c r="D40">
-        <v>739.5258325475651</v>
+        <v>736.5493921701518</v>
       </c>
       <c r="E40">
-        <v>213.398</v>
+        <v>219.819</v>
       </c>
       <c r="F40">
-        <v>243.998</v>
+        <v>250.419</v>
       </c>
       <c r="G40">
         <v>15.7</v>
@@ -4674,45 +4674,45 @@
         <v>100.2</v>
       </c>
       <c r="M40">
-        <v>13.053893</v>
+        <v>13.5977517</v>
       </c>
       <c r="N40">
-        <v>87.146107</v>
+        <v>86.6022483</v>
       </c>
       <c r="O40">
-        <v>21.78652675</v>
+        <v>21.650562075</v>
       </c>
       <c r="P40">
-        <v>65.35958024999999</v>
+        <v>64.951686225</v>
       </c>
       <c r="Q40">
-        <v>122.75958025</v>
+        <v>122.351686225</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08988660401415524</v>
+        <v>0.09048555253350343</v>
       </c>
       <c r="T40">
-        <v>0.8593299705887848</v>
+        <v>0.8710045920531737</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.675871098376553</v>
+        <v>7.368865251451826</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4720,22 +4720,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07107893704543709</v>
+        <v>0.07095267960209792</v>
       </c>
       <c r="C41">
-        <v>501.8303921701519</v>
+        <v>499.1066063286254</v>
       </c>
       <c r="D41">
-        <v>736.5493921701518</v>
+        <v>740.2466063286254</v>
       </c>
       <c r="E41">
-        <v>219.819</v>
+        <v>226.24</v>
       </c>
       <c r="F41">
-        <v>250.419</v>
+        <v>256.84</v>
       </c>
       <c r="G41">
         <v>15.7</v>
@@ -4756,28 +4756,28 @@
         <v>100.2</v>
       </c>
       <c r="M41">
-        <v>13.5977517</v>
+        <v>13.946412</v>
       </c>
       <c r="N41">
-        <v>86.6022483</v>
+        <v>86.25358800000001</v>
       </c>
       <c r="O41">
-        <v>21.650562075</v>
+        <v>21.563397</v>
       </c>
       <c r="P41">
-        <v>64.951686225</v>
+        <v>64.690191</v>
       </c>
       <c r="Q41">
-        <v>122.351686225</v>
+        <v>122.090191</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09048555253350343</v>
+        <v>0.09110446600349655</v>
       </c>
       <c r="T41">
-        <v>0.8710045920531737</v>
+        <v>0.8830683675663755</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.368865251451826</v>
+        <v>7.18464362016553</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4802,22 +4802,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07095267960209792</v>
+        <v>0.07082642215875877</v>
       </c>
       <c r="C42">
-        <v>499.1066063286254</v>
+        <v>496.4201251249058</v>
       </c>
       <c r="D42">
-        <v>740.2466063286254</v>
+        <v>743.9811251249058</v>
       </c>
       <c r="E42">
-        <v>226.24</v>
+        <v>232.661</v>
       </c>
       <c r="F42">
-        <v>256.84</v>
+        <v>263.261</v>
       </c>
       <c r="G42">
         <v>15.7</v>
@@ -4838,28 +4838,28 @@
         <v>100.2</v>
       </c>
       <c r="M42">
-        <v>13.946412</v>
+        <v>14.2950723</v>
       </c>
       <c r="N42">
-        <v>86.25358800000001</v>
+        <v>85.9049277</v>
       </c>
       <c r="O42">
-        <v>21.563397</v>
+        <v>21.476231925</v>
       </c>
       <c r="P42">
-        <v>64.690191</v>
+        <v>64.42869577499999</v>
       </c>
       <c r="Q42">
-        <v>122.090191</v>
+        <v>121.828695775</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09110446600349655</v>
+        <v>0.09174435959111657</v>
       </c>
       <c r="T42">
-        <v>0.8830683675663755</v>
+        <v>0.8955410846223979</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.18464362016553</v>
+        <v>7.009408409917591</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4884,22 +4884,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07082642215875877</v>
+        <v>0.07070016471541959</v>
       </c>
       <c r="C43">
-        <v>496.4201251249058</v>
+        <v>493.7715160236979</v>
       </c>
       <c r="D43">
-        <v>743.9811251249058</v>
+        <v>747.7535160236979</v>
       </c>
       <c r="E43">
-        <v>232.661</v>
+        <v>239.082</v>
       </c>
       <c r="F43">
-        <v>263.261</v>
+        <v>269.682</v>
       </c>
       <c r="G43">
         <v>15.7</v>
@@ -4920,28 +4920,28 @@
         <v>100.2</v>
       </c>
       <c r="M43">
-        <v>14.2950723</v>
+        <v>14.6437326</v>
       </c>
       <c r="N43">
-        <v>85.9049277</v>
+        <v>85.5562674</v>
       </c>
       <c r="O43">
-        <v>21.476231925</v>
+        <v>21.38906685</v>
       </c>
       <c r="P43">
-        <v>64.42869577499999</v>
+        <v>64.16720054999999</v>
       </c>
       <c r="Q43">
-        <v>121.828695775</v>
+        <v>121.56720055</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09174435959111657</v>
+        <v>0.09240631847486139</v>
       </c>
       <c r="T43">
-        <v>0.8955410846223979</v>
+        <v>0.908443895370007</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.009408409917591</v>
+        <v>6.842517733490981</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4966,22 +4966,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07070016471541961</v>
+        <v>0.07057390727208045</v>
       </c>
       <c r="C44">
-        <v>493.7715160236975</v>
+        <v>491.1613580577846</v>
       </c>
       <c r="D44">
-        <v>747.7535160236974</v>
+        <v>751.5643580577846</v>
       </c>
       <c r="E44">
-        <v>239.082</v>
+        <v>245.503</v>
       </c>
       <c r="F44">
-        <v>269.682</v>
+        <v>276.103</v>
       </c>
       <c r="G44">
         <v>15.7</v>
@@ -5002,28 +5002,28 @@
         <v>100.2</v>
       </c>
       <c r="M44">
-        <v>14.6437326</v>
+        <v>14.9923929</v>
       </c>
       <c r="N44">
-        <v>85.5562674</v>
+        <v>85.2076071</v>
       </c>
       <c r="O44">
-        <v>21.38906685</v>
+        <v>21.301901775</v>
       </c>
       <c r="P44">
-        <v>64.16720054999999</v>
+        <v>63.905705325</v>
       </c>
       <c r="Q44">
-        <v>121.56720055</v>
+        <v>121.305705325</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09240631847486139</v>
+        <v>0.09309150398610604</v>
       </c>
       <c r="T44">
-        <v>0.908443895370007</v>
+        <v>0.9217994363192866</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.842517733490981</v>
+        <v>6.683389414107471</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5048,22 +5048,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07057390727208045</v>
+        <v>0.0704476498287413</v>
       </c>
       <c r="C45">
-        <v>491.1613580577846</v>
+        <v>488.5902421243196</v>
       </c>
       <c r="D45">
-        <v>751.5643580577846</v>
+        <v>755.4142421243196</v>
       </c>
       <c r="E45">
-        <v>245.503</v>
+        <v>251.924</v>
       </c>
       <c r="F45">
-        <v>276.103</v>
+        <v>282.524</v>
       </c>
       <c r="G45">
         <v>15.7</v>
@@ -5084,28 +5084,28 @@
         <v>100.2</v>
       </c>
       <c r="M45">
-        <v>14.9923929</v>
+        <v>15.3410532</v>
       </c>
       <c r="N45">
-        <v>85.2076071</v>
+        <v>84.8589468</v>
       </c>
       <c r="O45">
-        <v>21.301901775</v>
+        <v>21.2147367</v>
       </c>
       <c r="P45">
-        <v>63.905705325</v>
+        <v>63.6442101</v>
       </c>
       <c r="Q45">
-        <v>121.305705325</v>
+        <v>121.0442101</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09309150398610604</v>
+        <v>0.09380116040846659</v>
       </c>
       <c r="T45">
-        <v>0.9217994363192866</v>
+        <v>0.935631960873898</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.683389414107471</v>
+        <v>6.531494200150482</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5130,22 +5130,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0704476498287413</v>
+        <v>0.07032139238540212</v>
       </c>
       <c r="C46">
-        <v>488.5902421243196</v>
+        <v>486.0587712902653</v>
       </c>
       <c r="D46">
-        <v>755.4142421243196</v>
+        <v>759.3037712902652</v>
       </c>
       <c r="E46">
-        <v>251.924</v>
+        <v>258.345</v>
       </c>
       <c r="F46">
-        <v>282.524</v>
+        <v>288.945</v>
       </c>
       <c r="G46">
         <v>15.7</v>
@@ -5166,28 +5166,28 @@
         <v>100.2</v>
       </c>
       <c r="M46">
-        <v>15.3410532</v>
+        <v>15.6897135</v>
       </c>
       <c r="N46">
-        <v>84.8589468</v>
+        <v>84.51028650000001</v>
       </c>
       <c r="O46">
-        <v>21.2147367</v>
+        <v>21.127571625</v>
       </c>
       <c r="P46">
-        <v>63.6442101</v>
+        <v>63.382714875</v>
       </c>
       <c r="Q46">
-        <v>121.0442101</v>
+        <v>120.782714875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09380116040846659</v>
+        <v>0.09453662251891295</v>
       </c>
       <c r="T46">
-        <v>0.935631960873898</v>
+        <v>0.9499674863214039</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.531494200150482</v>
+        <v>6.386349884591583</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5212,22 +5212,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07032139238540212</v>
+        <v>0.07019513494206296</v>
       </c>
       <c r="C47">
-        <v>486.0587712902653</v>
+        <v>483.5675611073156</v>
       </c>
       <c r="D47">
-        <v>759.3037712902652</v>
+        <v>763.2335611073156</v>
       </c>
       <c r="E47">
-        <v>258.345</v>
+        <v>264.766</v>
       </c>
       <c r="F47">
-        <v>288.945</v>
+        <v>295.366</v>
       </c>
       <c r="G47">
         <v>15.7</v>
@@ -5248,28 +5248,28 @@
         <v>100.2</v>
       </c>
       <c r="M47">
-        <v>15.6897135</v>
+        <v>16.0383738</v>
       </c>
       <c r="N47">
-        <v>84.51028650000001</v>
+        <v>84.1616262</v>
       </c>
       <c r="O47">
-        <v>21.127571625</v>
+        <v>21.04040655</v>
       </c>
       <c r="P47">
-        <v>63.382714875</v>
+        <v>63.12121965</v>
       </c>
       <c r="Q47">
-        <v>120.782714875</v>
+        <v>120.52121965</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09453662251891295</v>
+        <v>0.09529932396678326</v>
       </c>
       <c r="T47">
-        <v>0.9499674863214039</v>
+        <v>0.9648339571558547</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.386349884591583</v>
+        <v>6.247516191448287</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5294,22 +5294,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07019513494206296</v>
+        <v>0.0700688774987238</v>
       </c>
       <c r="C48">
-        <v>483.5675611073156</v>
+        <v>481.1172399366568</v>
       </c>
       <c r="D48">
-        <v>763.2335611073156</v>
+        <v>767.2042399366568</v>
       </c>
       <c r="E48">
-        <v>264.766</v>
+        <v>271.187</v>
       </c>
       <c r="F48">
-        <v>295.366</v>
+        <v>301.787</v>
       </c>
       <c r="G48">
         <v>15.7</v>
@@ -5330,28 +5330,28 @@
         <v>100.2</v>
       </c>
       <c r="M48">
-        <v>16.0383738</v>
+        <v>16.3870341</v>
       </c>
       <c r="N48">
-        <v>84.1616262</v>
+        <v>83.81296589999999</v>
       </c>
       <c r="O48">
-        <v>21.04040655</v>
+        <v>20.953241475</v>
       </c>
       <c r="P48">
-        <v>63.12121965</v>
+        <v>62.859724425</v>
       </c>
       <c r="Q48">
-        <v>120.52121965</v>
+        <v>120.259724425</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09529932396678326</v>
+        <v>0.09609080660136565</v>
       </c>
       <c r="T48">
-        <v>0.9648339571558547</v>
+        <v>0.9802614268897187</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5368,7 +5368,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.247516191448287</v>
+        <v>6.114590315034493</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5376,22 +5376,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0700688774987238</v>
+        <v>0.07030262005538465</v>
       </c>
       <c r="C49">
-        <v>481.1172399366568</v>
+        <v>467.377500956152</v>
       </c>
       <c r="D49">
-        <v>767.2042399366568</v>
+        <v>759.885500956152</v>
       </c>
       <c r="E49">
-        <v>271.187</v>
+        <v>277.608</v>
       </c>
       <c r="F49">
-        <v>301.787</v>
+        <v>308.208</v>
       </c>
       <c r="G49">
         <v>15.7</v>
@@ -5412,45 +5412,45 @@
         <v>100.2</v>
       </c>
       <c r="M49">
-        <v>16.3870341</v>
+        <v>17.0439024</v>
       </c>
       <c r="N49">
-        <v>83.81296589999999</v>
+        <v>83.15609760000001</v>
       </c>
       <c r="O49">
-        <v>20.953241475</v>
+        <v>20.7890244</v>
       </c>
       <c r="P49">
-        <v>62.859724425</v>
+        <v>62.36707320000001</v>
       </c>
       <c r="Q49">
-        <v>120.259724425</v>
+        <v>119.7670732</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09609080660136565</v>
+        <v>0.09691273087573969</v>
       </c>
       <c r="T49">
-        <v>0.9802614268897187</v>
+        <v>0.996282260844116</v>
       </c>
       <c r="U49">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>6.114590315034493</v>
+        <v>5.878935331148107</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5458,22 +5458,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07030262005538464</v>
+        <v>0.07018386261204547</v>
       </c>
       <c r="C50">
-        <v>467.3775009561525</v>
+        <v>464.6573936637532</v>
       </c>
       <c r="D50">
-        <v>759.8855009561524</v>
+        <v>763.5863936637531</v>
       </c>
       <c r="E50">
-        <v>277.608</v>
+        <v>284.029</v>
       </c>
       <c r="F50">
-        <v>308.208</v>
+        <v>314.629</v>
       </c>
       <c r="G50">
         <v>15.7</v>
@@ -5494,28 +5494,28 @@
         <v>100.2</v>
       </c>
       <c r="M50">
-        <v>17.0439024</v>
+        <v>17.3989837</v>
       </c>
       <c r="N50">
-        <v>83.15609760000001</v>
+        <v>82.8010163</v>
       </c>
       <c r="O50">
-        <v>20.7890244</v>
+        <v>20.700254075</v>
       </c>
       <c r="P50">
-        <v>62.36707320000001</v>
+        <v>62.100762225</v>
       </c>
       <c r="Q50">
-        <v>119.7670732</v>
+        <v>119.500762225</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09691273087573969</v>
+        <v>0.09776688747459897</v>
       </c>
       <c r="T50">
-        <v>0.996282260844116</v>
+        <v>1.012931362796725</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.878935331148107</v>
+        <v>5.758957059083858</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5540,22 +5540,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07018386261204547</v>
+        <v>0.07006510516870632</v>
       </c>
       <c r="C51">
-        <v>464.6573936637532</v>
+        <v>461.9735119350153</v>
       </c>
       <c r="D51">
-        <v>763.5863936637531</v>
+        <v>767.3235119350153</v>
       </c>
       <c r="E51">
-        <v>284.029</v>
+        <v>290.45</v>
       </c>
       <c r="F51">
-        <v>314.629</v>
+        <v>321.05</v>
       </c>
       <c r="G51">
         <v>15.7</v>
@@ -5576,28 +5576,28 @@
         <v>100.2</v>
       </c>
       <c r="M51">
-        <v>17.3989837</v>
+        <v>17.754065</v>
       </c>
       <c r="N51">
-        <v>82.8010163</v>
+        <v>82.44593500000001</v>
       </c>
       <c r="O51">
-        <v>20.700254075</v>
+        <v>20.61148375</v>
       </c>
       <c r="P51">
-        <v>62.100762225</v>
+        <v>61.83445125</v>
       </c>
       <c r="Q51">
-        <v>119.500762225</v>
+        <v>119.23445125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09776688747459897</v>
+        <v>0.09865521033741263</v>
       </c>
       <c r="T51">
-        <v>1.012931362796725</v>
+        <v>1.030246428827438</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.758957059083858</v>
+        <v>5.643777917902182</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5622,22 +5622,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07006510516870632</v>
+        <v>0.06994634772536716</v>
       </c>
       <c r="C52">
-        <v>461.9735119350153</v>
+        <v>459.3263902675837</v>
       </c>
       <c r="D52">
-        <v>767.3235119350153</v>
+        <v>771.0973902675837</v>
       </c>
       <c r="E52">
-        <v>290.45</v>
+        <v>296.871</v>
       </c>
       <c r="F52">
-        <v>321.05</v>
+        <v>327.471</v>
       </c>
       <c r="G52">
         <v>15.7</v>
@@ -5658,28 +5658,28 @@
         <v>100.2</v>
       </c>
       <c r="M52">
-        <v>17.754065</v>
+        <v>18.1091463</v>
       </c>
       <c r="N52">
-        <v>82.44593500000001</v>
+        <v>82.0908537</v>
       </c>
       <c r="O52">
-        <v>20.61148375</v>
+        <v>20.522713425</v>
       </c>
       <c r="P52">
-        <v>61.83445125</v>
+        <v>61.568140275</v>
       </c>
       <c r="Q52">
-        <v>119.23445125</v>
+        <v>118.968140275</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09865521033741263</v>
+        <v>0.09957979127625952</v>
       </c>
       <c r="T52">
-        <v>1.030246428827438</v>
+        <v>1.04826823224716</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.643777917902182</v>
+        <v>5.533115605786452</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5704,22 +5704,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06994634772536716</v>
+        <v>0.06982759028202799</v>
       </c>
       <c r="C53">
-        <v>459.3263902675837</v>
+        <v>456.7165737262171</v>
       </c>
       <c r="D53">
-        <v>771.0973902675837</v>
+        <v>774.908573726217</v>
       </c>
       <c r="E53">
-        <v>296.871</v>
+        <v>303.292</v>
       </c>
       <c r="F53">
-        <v>327.471</v>
+        <v>333.892</v>
       </c>
       <c r="G53">
         <v>15.7</v>
@@ -5740,28 +5740,28 @@
         <v>100.2</v>
       </c>
       <c r="M53">
-        <v>18.1091463</v>
+        <v>18.4642276</v>
       </c>
       <c r="N53">
-        <v>82.0908537</v>
+        <v>81.7357724</v>
       </c>
       <c r="O53">
-        <v>20.522713425</v>
+        <v>20.4339431</v>
       </c>
       <c r="P53">
-        <v>61.568140275</v>
+        <v>61.3018293</v>
       </c>
       <c r="Q53">
-        <v>118.968140275</v>
+        <v>118.7018293</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09957979127625952</v>
+        <v>0.1005428964208917</v>
       </c>
       <c r="T53">
-        <v>1.04826823224716</v>
+        <v>1.067040944142704</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.533115605786452</v>
+        <v>5.426709536444405</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5786,22 +5786,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06982759028202799</v>
+        <v>0.06970883283868884</v>
       </c>
       <c r="C54">
-        <v>456.7165737262171</v>
+        <v>454.1446182052264</v>
       </c>
       <c r="D54">
-        <v>774.908573726217</v>
+        <v>778.7576182052264</v>
       </c>
       <c r="E54">
-        <v>303.292</v>
+        <v>309.713</v>
       </c>
       <c r="F54">
-        <v>333.892</v>
+        <v>340.313</v>
       </c>
       <c r="G54">
         <v>15.7</v>
@@ -5822,28 +5822,28 @@
         <v>100.2</v>
       </c>
       <c r="M54">
-        <v>18.4642276</v>
+        <v>18.8193089</v>
       </c>
       <c r="N54">
-        <v>81.7357724</v>
+        <v>81.38069110000001</v>
       </c>
       <c r="O54">
-        <v>20.4339431</v>
+        <v>20.345172775</v>
       </c>
       <c r="P54">
-        <v>61.3018293</v>
+        <v>61.03551832500001</v>
       </c>
       <c r="Q54">
-        <v>118.7018293</v>
+        <v>118.435518325</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1005428964208917</v>
+        <v>0.1015469847631677</v>
       </c>
       <c r="T54">
-        <v>1.067040944142704</v>
+        <v>1.086612494842313</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.426709536444405</v>
+        <v>5.324318790473757</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5868,22 +5868,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06970883283868884</v>
+        <v>0.06959007539534967</v>
       </c>
       <c r="C55">
-        <v>454.1446182052264</v>
+        <v>451.6110906987785</v>
       </c>
       <c r="D55">
-        <v>778.7576182052264</v>
+        <v>782.6450906987785</v>
       </c>
       <c r="E55">
-        <v>309.713</v>
+        <v>316.134</v>
       </c>
       <c r="F55">
-        <v>340.313</v>
+        <v>346.734</v>
       </c>
       <c r="G55">
         <v>15.7</v>
@@ -5904,28 +5904,28 @@
         <v>100.2</v>
       </c>
       <c r="M55">
-        <v>18.8193089</v>
+        <v>19.1743902</v>
       </c>
       <c r="N55">
-        <v>81.38069110000001</v>
+        <v>81.0256098</v>
       </c>
       <c r="O55">
-        <v>20.345172775</v>
+        <v>20.25640245</v>
       </c>
       <c r="P55">
-        <v>61.03551832500001</v>
+        <v>60.76920735</v>
       </c>
       <c r="Q55">
-        <v>118.435518325</v>
+        <v>118.16920735</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1015469847631677</v>
+        <v>0.1025947291203254</v>
       </c>
       <c r="T55">
-        <v>1.086612494842313</v>
+        <v>1.107034982528862</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.324318790473757</v>
+        <v>5.225720294353872</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5950,22 +5950,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06959007539534967</v>
+        <v>0.06947131795201052</v>
       </c>
       <c r="C56">
-        <v>451.6110906987785</v>
+        <v>449.1165695793274</v>
       </c>
       <c r="D56">
-        <v>782.6450906987785</v>
+        <v>786.5715695793274</v>
       </c>
       <c r="E56">
-        <v>316.134</v>
+        <v>322.555</v>
       </c>
       <c r="F56">
-        <v>346.734</v>
+        <v>353.155</v>
       </c>
       <c r="G56">
         <v>15.7</v>
@@ -5986,28 +5986,28 @@
         <v>100.2</v>
       </c>
       <c r="M56">
-        <v>19.1743902</v>
+        <v>19.5294715</v>
       </c>
       <c r="N56">
-        <v>81.0256098</v>
+        <v>80.6705285</v>
       </c>
       <c r="O56">
-        <v>20.25640245</v>
+        <v>20.167632125</v>
       </c>
       <c r="P56">
-        <v>60.76920735</v>
+        <v>60.50289637500001</v>
       </c>
       <c r="Q56">
-        <v>118.16920735</v>
+        <v>117.902896375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1025947291203254</v>
+        <v>0.1036890398933567</v>
       </c>
       <c r="T56">
-        <v>1.107034982528862</v>
+        <v>1.128365136334813</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.225720294353872</v>
+        <v>5.130707198092892</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6032,22 +6032,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06947131795201052</v>
+        <v>0.06935256050867135</v>
       </c>
       <c r="C57">
-        <v>449.1165695793274</v>
+        <v>446.6616448844785</v>
       </c>
       <c r="D57">
-        <v>786.5715695793274</v>
+        <v>790.5376448844785</v>
       </c>
       <c r="E57">
-        <v>322.555</v>
+        <v>328.976</v>
       </c>
       <c r="F57">
-        <v>353.155</v>
+        <v>359.576</v>
       </c>
       <c r="G57">
         <v>15.7</v>
@@ -6068,28 +6068,28 @@
         <v>100.2</v>
       </c>
       <c r="M57">
-        <v>19.5294715</v>
+        <v>19.8845528</v>
       </c>
       <c r="N57">
-        <v>80.6705285</v>
+        <v>80.31544719999999</v>
       </c>
       <c r="O57">
-        <v>20.167632125</v>
+        <v>20.0788618</v>
       </c>
       <c r="P57">
-        <v>60.50289637500001</v>
+        <v>60.2365854</v>
       </c>
       <c r="Q57">
-        <v>117.902896375</v>
+        <v>117.6365854</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1036890398933567</v>
+        <v>0.1048330920651622</v>
       </c>
       <c r="T57">
-        <v>1.128365136334813</v>
+        <v>1.150664842586489</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.130707198092892</v>
+        <v>5.039087426698376</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6114,22 +6114,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06935256050867135</v>
+        <v>0.06923380306533219</v>
       </c>
       <c r="C58">
-        <v>446.6616448844785</v>
+        <v>444.2469186125668</v>
       </c>
       <c r="D58">
-        <v>790.5376448844785</v>
+        <v>794.5439186125668</v>
       </c>
       <c r="E58">
-        <v>328.976</v>
+        <v>335.397</v>
       </c>
       <c r="F58">
-        <v>359.576</v>
+        <v>365.9970000000001</v>
       </c>
       <c r="G58">
         <v>15.7</v>
@@ -6150,28 +6150,28 @@
         <v>100.2</v>
       </c>
       <c r="M58">
-        <v>19.8845528</v>
+        <v>20.2396341</v>
       </c>
       <c r="N58">
-        <v>80.31544719999999</v>
+        <v>79.9603659</v>
       </c>
       <c r="O58">
-        <v>20.0788618</v>
+        <v>19.990091475</v>
       </c>
       <c r="P58">
-        <v>60.2365854</v>
+        <v>59.970274425</v>
       </c>
       <c r="Q58">
-        <v>117.6365854</v>
+        <v>117.370274425</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1048330920651622</v>
+        <v>0.1060303559658888</v>
       </c>
       <c r="T58">
-        <v>1.150664842586489</v>
+        <v>1.174001744477778</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.039087426698376</v>
+        <v>4.95068238412472</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6196,22 +6196,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06923380306533219</v>
+        <v>0.06911504562199303</v>
       </c>
       <c r="C59">
-        <v>444.2469186125668</v>
+        <v>441.8730050272769</v>
       </c>
       <c r="D59">
-        <v>794.5439186125668</v>
+        <v>798.5910050272769</v>
       </c>
       <c r="E59">
-        <v>335.397</v>
+        <v>341.818</v>
       </c>
       <c r="F59">
-        <v>365.9970000000001</v>
+        <v>372.4180000000001</v>
       </c>
       <c r="G59">
         <v>15.7</v>
@@ -6232,28 +6232,28 @@
         <v>100.2</v>
       </c>
       <c r="M59">
-        <v>20.2396341</v>
+        <v>20.59471540000001</v>
       </c>
       <c r="N59">
-        <v>79.9603659</v>
+        <v>79.6052846</v>
       </c>
       <c r="O59">
-        <v>19.990091475</v>
+        <v>19.90132115</v>
       </c>
       <c r="P59">
-        <v>59.970274425</v>
+        <v>59.70396345</v>
       </c>
       <c r="Q59">
-        <v>117.370274425</v>
+        <v>117.10396345</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1060303559658888</v>
+        <v>0.1072846324333168</v>
       </c>
       <c r="T59">
-        <v>1.174001744477778</v>
+        <v>1.19844992741151</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.95068238412472</v>
+        <v>4.865325791294984</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6278,22 +6278,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06911504562199303</v>
+        <v>0.06899628817865387</v>
       </c>
       <c r="C60">
-        <v>441.8730050272769</v>
+        <v>439.5405309716113</v>
       </c>
       <c r="D60">
-        <v>798.5910050272769</v>
+        <v>802.6795309716113</v>
       </c>
       <c r="E60">
-        <v>341.818</v>
+        <v>348.239</v>
       </c>
       <c r="F60">
-        <v>372.418</v>
+        <v>378.839</v>
       </c>
       <c r="G60">
         <v>15.7</v>
@@ -6314,28 +6314,28 @@
         <v>100.2</v>
       </c>
       <c r="M60">
-        <v>20.5947154</v>
+        <v>20.9497967</v>
       </c>
       <c r="N60">
-        <v>79.6052846</v>
+        <v>79.25020330000001</v>
       </c>
       <c r="O60">
-        <v>19.90132115</v>
+        <v>19.812550825</v>
       </c>
       <c r="P60">
-        <v>59.70396345</v>
+        <v>59.43765247500001</v>
       </c>
       <c r="Q60">
-        <v>117.10396345</v>
+        <v>116.837652475</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1072846324333167</v>
+        <v>0.108600093118668</v>
       </c>
       <c r="T60">
-        <v>1.198449927411509</v>
+        <v>1.224090704634691</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.865325791294984</v>
+        <v>4.782862642289984</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6360,22 +6360,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06899628817865387</v>
+        <v>0.0688775307353147</v>
       </c>
       <c r="C61">
-        <v>439.5405309716113</v>
+        <v>437.2501361915624</v>
       </c>
       <c r="D61">
-        <v>802.6795309716113</v>
+        <v>806.8101361915624</v>
       </c>
       <c r="E61">
-        <v>348.239</v>
+        <v>354.66</v>
       </c>
       <c r="F61">
-        <v>378.839</v>
+        <v>385.26</v>
       </c>
       <c r="G61">
         <v>15.7</v>
@@ -6396,28 +6396,28 @@
         <v>100.2</v>
       </c>
       <c r="M61">
-        <v>20.9497967</v>
+        <v>21.304878</v>
       </c>
       <c r="N61">
-        <v>79.25020330000001</v>
+        <v>78.895122</v>
       </c>
       <c r="O61">
-        <v>19.812550825</v>
+        <v>19.7237805</v>
       </c>
       <c r="P61">
-        <v>59.43765247500001</v>
+        <v>59.1713415</v>
       </c>
       <c r="Q61">
-        <v>116.837652475</v>
+        <v>116.5713415</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.108600093118668</v>
+        <v>0.1099813268382868</v>
       </c>
       <c r="T61">
-        <v>1.224090704634691</v>
+        <v>1.251013520719032</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.782862642289984</v>
+        <v>4.703148264918485</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6442,22 +6442,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0688775307353147</v>
+        <v>0.06875877329197555</v>
       </c>
       <c r="C62">
-        <v>437.2501361915624</v>
+        <v>435.0024736698203</v>
       </c>
       <c r="D62">
-        <v>806.8101361915624</v>
+        <v>810.9834736698202</v>
       </c>
       <c r="E62">
-        <v>354.66</v>
+        <v>361.081</v>
       </c>
       <c r="F62">
-        <v>385.26</v>
+        <v>391.681</v>
       </c>
       <c r="G62">
         <v>15.7</v>
@@ -6478,28 +6478,28 @@
         <v>100.2</v>
       </c>
       <c r="M62">
-        <v>21.304878</v>
+        <v>21.6599593</v>
       </c>
       <c r="N62">
-        <v>78.895122</v>
+        <v>78.54004070000001</v>
       </c>
       <c r="O62">
-        <v>19.7237805</v>
+        <v>19.635010175</v>
       </c>
       <c r="P62">
-        <v>59.1713415</v>
+        <v>58.905030525</v>
       </c>
       <c r="Q62">
-        <v>116.5713415</v>
+        <v>116.305030525</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1099813268382868</v>
+        <v>0.1114333930563476</v>
       </c>
       <c r="T62">
-        <v>1.251013520719032</v>
+        <v>1.279316994038467</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.703148264918485</v>
+        <v>4.626047473690313</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6524,22 +6524,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06875877329197555</v>
+        <v>0.06864001584863638</v>
       </c>
       <c r="C63">
-        <v>435.0024736698203</v>
+        <v>432.7982099699</v>
       </c>
       <c r="D63">
-        <v>810.9834736698202</v>
+        <v>815.2002099699</v>
       </c>
       <c r="E63">
-        <v>361.081</v>
+        <v>367.502</v>
       </c>
       <c r="F63">
-        <v>391.681</v>
+        <v>398.102</v>
       </c>
       <c r="G63">
         <v>15.7</v>
@@ -6560,28 +6560,28 @@
         <v>100.2</v>
       </c>
       <c r="M63">
-        <v>21.6599593</v>
+        <v>22.0150406</v>
       </c>
       <c r="N63">
-        <v>78.54004070000001</v>
+        <v>78.1849594</v>
       </c>
       <c r="O63">
-        <v>19.635010175</v>
+        <v>19.54623985</v>
       </c>
       <c r="P63">
-        <v>58.905030525</v>
+        <v>58.63871955</v>
       </c>
       <c r="Q63">
-        <v>116.305030525</v>
+        <v>116.03871955</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1114333930563476</v>
+        <v>0.112961883812201</v>
       </c>
       <c r="T63">
-        <v>1.279316994038467</v>
+        <v>1.309110123848399</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.626047473690313</v>
+        <v>4.551433804759824</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6606,22 +6606,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06864001584863638</v>
+        <v>0.06970250840529724</v>
       </c>
       <c r="C64">
-        <v>432.7982099699</v>
+        <v>390.1406719214738</v>
       </c>
       <c r="D64">
-        <v>815.2002099699</v>
+        <v>778.9636719214737</v>
       </c>
       <c r="E64">
-        <v>367.502</v>
+        <v>373.923</v>
       </c>
       <c r="F64">
-        <v>398.102</v>
+        <v>404.523</v>
       </c>
       <c r="G64">
         <v>15.7</v>
@@ -6642,45 +6642,45 @@
         <v>100.2</v>
       </c>
       <c r="M64">
-        <v>22.0150406</v>
+        <v>23.3814294</v>
       </c>
       <c r="N64">
-        <v>78.1849594</v>
+        <v>76.8185706</v>
       </c>
       <c r="O64">
-        <v>19.54623985</v>
+        <v>19.20464265</v>
       </c>
       <c r="P64">
-        <v>58.63871955</v>
+        <v>57.61392795</v>
       </c>
       <c r="Q64">
-        <v>116.03871955</v>
+        <v>115.01392795</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.112961883812201</v>
+        <v>0.1145729956899925</v>
       </c>
       <c r="T64">
-        <v>1.309110123848399</v>
+        <v>1.340513693107516</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.551433804759824</v>
+        <v>4.285452282913036</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6688,22 +6688,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06970250840529724</v>
+        <v>0.06960250096195807</v>
       </c>
       <c r="C65">
-        <v>390.1406719214738</v>
+        <v>386.9925282237363</v>
       </c>
       <c r="D65">
-        <v>778.9636719214737</v>
+        <v>782.2365282237363</v>
       </c>
       <c r="E65">
-        <v>373.923</v>
+        <v>380.344</v>
       </c>
       <c r="F65">
-        <v>404.523</v>
+        <v>410.944</v>
       </c>
       <c r="G65">
         <v>15.7</v>
@@ -6724,28 +6724,28 @@
         <v>100.2</v>
       </c>
       <c r="M65">
-        <v>23.3814294</v>
+        <v>23.7525632</v>
       </c>
       <c r="N65">
-        <v>76.8185706</v>
+        <v>76.44743679999999</v>
       </c>
       <c r="O65">
-        <v>19.20464265</v>
+        <v>19.1118592</v>
       </c>
       <c r="P65">
-        <v>57.61392795</v>
+        <v>57.33557759999999</v>
       </c>
       <c r="Q65">
-        <v>115.01392795</v>
+        <v>114.7355776</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1145729956899925</v>
+        <v>0.1162736137832169</v>
       </c>
       <c r="T65">
-        <v>1.340513693107516</v>
+        <v>1.373661905103251</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.285452282913036</v>
+        <v>4.21849209099252</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6770,22 +6770,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06960250096195807</v>
+        <v>0.0695024935186189</v>
       </c>
       <c r="C66">
-        <v>386.9925282237363</v>
+        <v>383.8720027165451</v>
       </c>
       <c r="D66">
-        <v>782.2365282237363</v>
+        <v>785.5370027165451</v>
       </c>
       <c r="E66">
-        <v>380.344</v>
+        <v>386.765</v>
       </c>
       <c r="F66">
-        <v>410.944</v>
+        <v>417.365</v>
       </c>
       <c r="G66">
         <v>15.7</v>
@@ -6806,28 +6806,28 @@
         <v>100.2</v>
       </c>
       <c r="M66">
-        <v>23.7525632</v>
+        <v>24.123697</v>
       </c>
       <c r="N66">
-        <v>76.44743679999999</v>
+        <v>76.076303</v>
       </c>
       <c r="O66">
-        <v>19.1118592</v>
+        <v>19.01907575</v>
       </c>
       <c r="P66">
-        <v>57.33557759999999</v>
+        <v>57.05722725</v>
       </c>
       <c r="Q66">
-        <v>114.7355776</v>
+        <v>114.45722725</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1162736137832169</v>
+        <v>0.1180714100531969</v>
       </c>
       <c r="T66">
-        <v>1.373661905103251</v>
+        <v>1.408704300641599</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.21849209099252</v>
+        <v>4.153592212669558</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6852,22 +6852,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0695024935186189</v>
+        <v>0.06940248607527974</v>
       </c>
       <c r="C67">
-        <v>383.8720027165451</v>
+        <v>380.7794464677422</v>
       </c>
       <c r="D67">
-        <v>785.5370027165451</v>
+        <v>788.8654464677422</v>
       </c>
       <c r="E67">
-        <v>386.765</v>
+        <v>393.186</v>
       </c>
       <c r="F67">
-        <v>417.365</v>
+        <v>423.7860000000001</v>
       </c>
       <c r="G67">
         <v>15.7</v>
@@ -6888,28 +6888,28 @@
         <v>100.2</v>
       </c>
       <c r="M67">
-        <v>24.123697</v>
+        <v>24.49483080000001</v>
       </c>
       <c r="N67">
-        <v>76.076303</v>
+        <v>75.7051692</v>
       </c>
       <c r="O67">
-        <v>19.01907575</v>
+        <v>18.9262923</v>
       </c>
       <c r="P67">
-        <v>57.05722725</v>
+        <v>56.7788769</v>
       </c>
       <c r="Q67">
-        <v>114.45722725</v>
+        <v>114.1788769</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1180714100531969</v>
+        <v>0.1199749590449404</v>
       </c>
       <c r="T67">
-        <v>1.408704300641599</v>
+        <v>1.445808013564556</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.153592212669558</v>
+        <v>4.09065899732608</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6934,22 +6934,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06940248607527974</v>
+        <v>0.06930247863194058</v>
       </c>
       <c r="C68">
-        <v>380.7794464677422</v>
+        <v>377.7152165206091</v>
       </c>
       <c r="D68">
-        <v>788.8654464677422</v>
+        <v>792.2222165206091</v>
       </c>
       <c r="E68">
-        <v>393.186</v>
+        <v>399.607</v>
       </c>
       <c r="F68">
-        <v>423.7860000000001</v>
+        <v>430.2070000000001</v>
       </c>
       <c r="G68">
         <v>15.7</v>
@@ -6970,28 +6970,28 @@
         <v>100.2</v>
       </c>
       <c r="M68">
-        <v>24.49483080000001</v>
+        <v>24.86596460000001</v>
       </c>
       <c r="N68">
-        <v>75.7051692</v>
+        <v>75.3340354</v>
       </c>
       <c r="O68">
-        <v>18.9262923</v>
+        <v>18.83350885</v>
       </c>
       <c r="P68">
-        <v>56.7788769</v>
+        <v>56.50052655</v>
       </c>
       <c r="Q68">
-        <v>114.1788769</v>
+        <v>113.90052655</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1199749590449404</v>
+        <v>0.1219938746422442</v>
       </c>
       <c r="T68">
-        <v>1.445808013564556</v>
+        <v>1.485160436361632</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.09065899732608</v>
+        <v>4.02960438542569</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7016,22 +7016,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06930247863194058</v>
+        <v>0.07098747118860144</v>
       </c>
       <c r="C69">
-        <v>377.7152165206091</v>
+        <v>318.2960997957078</v>
       </c>
       <c r="D69">
-        <v>792.2222165206091</v>
+        <v>739.2240997957078</v>
       </c>
       <c r="E69">
-        <v>399.607</v>
+        <v>406.028</v>
       </c>
       <c r="F69">
-        <v>430.2070000000001</v>
+        <v>436.628</v>
       </c>
       <c r="G69">
         <v>15.7</v>
@@ -7052,45 +7052,45 @@
         <v>100.2</v>
       </c>
       <c r="M69">
-        <v>24.86596460000001</v>
+        <v>26.7652964</v>
       </c>
       <c r="N69">
-        <v>75.3340354</v>
+        <v>73.43470360000001</v>
       </c>
       <c r="O69">
-        <v>18.83350885</v>
+        <v>18.3586759</v>
       </c>
       <c r="P69">
-        <v>56.50052655</v>
+        <v>55.0760277</v>
       </c>
       <c r="Q69">
-        <v>113.90052655</v>
+        <v>112.4760277</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1219938746422442</v>
+        <v>0.1241389724643795</v>
       </c>
       <c r="T69">
-        <v>1.485160436361632</v>
+        <v>1.526972385583525</v>
       </c>
       <c r="U69">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.02960438542569</v>
+        <v>3.743653666394668</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7098,22 +7098,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07098747118860144</v>
+        <v>0.07091371374526226</v>
       </c>
       <c r="C70">
-        <v>318.2960997957078</v>
+        <v>314.0461558254407</v>
       </c>
       <c r="D70">
-        <v>739.2240997957078</v>
+        <v>741.3951558254407</v>
       </c>
       <c r="E70">
-        <v>406.028</v>
+        <v>412.449</v>
       </c>
       <c r="F70">
-        <v>436.628</v>
+        <v>443.049</v>
       </c>
       <c r="G70">
         <v>15.7</v>
@@ -7134,28 +7134,28 @@
         <v>100.2</v>
       </c>
       <c r="M70">
-        <v>26.7652964</v>
+        <v>27.1589037</v>
       </c>
       <c r="N70">
-        <v>73.43470360000001</v>
+        <v>73.04109629999999</v>
       </c>
       <c r="O70">
-        <v>18.3586759</v>
+        <v>18.260274075</v>
       </c>
       <c r="P70">
-        <v>55.0760277</v>
+        <v>54.78082222499999</v>
       </c>
       <c r="Q70">
-        <v>112.4760277</v>
+        <v>112.180822225</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1241389724643795</v>
+        <v>0.1264224636943944</v>
       </c>
       <c r="T70">
-        <v>1.526972385583525</v>
+        <v>1.571481879916507</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.743653666394668</v>
+        <v>3.689397816157063</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7180,22 +7180,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07091371374526226</v>
+        <v>0.07083995630192311</v>
       </c>
       <c r="C71">
-        <v>314.0461558254407</v>
+        <v>309.8090019367662</v>
       </c>
       <c r="D71">
-        <v>741.3951558254407</v>
+        <v>743.5790019367662</v>
       </c>
       <c r="E71">
-        <v>412.449</v>
+        <v>418.8700000000001</v>
       </c>
       <c r="F71">
-        <v>443.049</v>
+        <v>449.4700000000001</v>
       </c>
       <c r="G71">
         <v>15.7</v>
@@ -7216,28 +7216,28 @@
         <v>100.2</v>
       </c>
       <c r="M71">
-        <v>27.1589037</v>
+        <v>27.55251100000001</v>
       </c>
       <c r="N71">
-        <v>73.04109629999999</v>
+        <v>72.64748899999999</v>
       </c>
       <c r="O71">
-        <v>18.260274075</v>
+        <v>18.16187225</v>
       </c>
       <c r="P71">
-        <v>54.78082222499999</v>
+        <v>54.48561674999999</v>
       </c>
       <c r="Q71">
-        <v>112.180822225</v>
+        <v>111.88561675</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1264224636943944</v>
+        <v>0.128858187673077</v>
       </c>
       <c r="T71">
-        <v>1.571481879916507</v>
+        <v>1.618958673871689</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.689397816157063</v>
+        <v>3.636692133069105</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7262,22 +7262,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07083995630192311</v>
+        <v>0.07076619885858394</v>
       </c>
       <c r="C72">
-        <v>309.8090019367662</v>
+        <v>305.5847514865955</v>
       </c>
       <c r="D72">
-        <v>743.5790019367662</v>
+        <v>745.7757514865955</v>
       </c>
       <c r="E72">
-        <v>418.8700000000001</v>
+        <v>425.2910000000001</v>
       </c>
       <c r="F72">
-        <v>449.4700000000001</v>
+        <v>455.8910000000001</v>
       </c>
       <c r="G72">
         <v>15.7</v>
@@ -7298,28 +7298,28 @@
         <v>100.2</v>
       </c>
       <c r="M72">
-        <v>27.55251100000001</v>
+        <v>27.94611830000001</v>
       </c>
       <c r="N72">
-        <v>72.64748899999999</v>
+        <v>72.25388169999999</v>
       </c>
       <c r="O72">
-        <v>18.16187225</v>
+        <v>18.063470425</v>
       </c>
       <c r="P72">
-        <v>54.48561674999999</v>
+        <v>54.190411275</v>
       </c>
       <c r="Q72">
-        <v>111.88561675</v>
+        <v>111.590411275</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.128858187673077</v>
+        <v>0.1314618926158067</v>
       </c>
       <c r="T72">
-        <v>1.618958673871689</v>
+        <v>1.669709729478952</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.636692133069105</v>
+        <v>3.585471117110385</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7344,22 +7344,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07076619885858394</v>
+        <v>0.07069244141524478</v>
       </c>
       <c r="C73">
-        <v>305.5847514865955</v>
+        <v>301.373519175365</v>
       </c>
       <c r="D73">
-        <v>745.7757514865955</v>
+        <v>747.985519175365</v>
       </c>
       <c r="E73">
-        <v>425.291</v>
+        <v>431.712</v>
       </c>
       <c r="F73">
-        <v>455.891</v>
+        <v>462.312</v>
       </c>
       <c r="G73">
         <v>15.7</v>
@@ -7380,28 +7380,28 @@
         <v>100.2</v>
       </c>
       <c r="M73">
-        <v>27.9461183</v>
+        <v>28.3397256</v>
       </c>
       <c r="N73">
-        <v>72.25388169999999</v>
+        <v>71.86027440000001</v>
       </c>
       <c r="O73">
-        <v>18.063470425</v>
+        <v>17.9650686</v>
       </c>
       <c r="P73">
-        <v>54.190411275</v>
+        <v>53.89520580000001</v>
       </c>
       <c r="Q73">
-        <v>111.590411275</v>
+        <v>111.2952058</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1314618926158067</v>
+        <v>0.1342515764830171</v>
       </c>
       <c r="T73">
-        <v>1.669709729478951</v>
+        <v>1.724085860486733</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.585471117110385</v>
+        <v>3.53567290715052</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7426,22 +7426,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07069244141524478</v>
+        <v>0.07215168397190561</v>
       </c>
       <c r="C74">
-        <v>301.373519175365</v>
+        <v>253.5323085159471</v>
       </c>
       <c r="D74">
-        <v>747.985519175365</v>
+        <v>706.5653085159471</v>
       </c>
       <c r="E74">
-        <v>431.712</v>
+        <v>438.133</v>
       </c>
       <c r="F74">
-        <v>462.312</v>
+        <v>468.733</v>
       </c>
       <c r="G74">
         <v>15.7</v>
@@ -7462,45 +7462,45 @@
         <v>100.2</v>
       </c>
       <c r="M74">
-        <v>28.3397256</v>
+        <v>30.0457853</v>
       </c>
       <c r="N74">
-        <v>71.86027440000001</v>
+        <v>70.1542147</v>
       </c>
       <c r="O74">
-        <v>17.9650686</v>
+        <v>17.538553675</v>
       </c>
       <c r="P74">
-        <v>53.89520580000001</v>
+        <v>52.61566102499999</v>
       </c>
       <c r="Q74">
-        <v>111.2952058</v>
+        <v>110.015661025</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1342515764830171</v>
+        <v>0.1372479035996504</v>
       </c>
       <c r="T74">
-        <v>1.724085860486733</v>
+        <v>1.782489853050647</v>
       </c>
       <c r="U74">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.53567290715052</v>
+        <v>3.334910337657242</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7508,22 +7508,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07215168397190561</v>
+        <v>0.07209892652856646</v>
       </c>
       <c r="C75">
-        <v>253.5323085159471</v>
+        <v>248.5287267968395</v>
       </c>
       <c r="D75">
-        <v>706.5653085159471</v>
+        <v>707.9827267968394</v>
       </c>
       <c r="E75">
-        <v>438.133</v>
+        <v>444.554</v>
       </c>
       <c r="F75">
-        <v>468.733</v>
+        <v>475.154</v>
       </c>
       <c r="G75">
         <v>15.7</v>
@@ -7544,28 +7544,28 @@
         <v>100.2</v>
       </c>
       <c r="M75">
-        <v>30.0457853</v>
+        <v>30.4573714</v>
       </c>
       <c r="N75">
-        <v>70.1542147</v>
+        <v>69.7426286</v>
       </c>
       <c r="O75">
-        <v>17.538553675</v>
+        <v>17.43565715</v>
       </c>
       <c r="P75">
-        <v>52.61566102499999</v>
+        <v>52.30697145000001</v>
       </c>
       <c r="Q75">
-        <v>110.015661025</v>
+        <v>109.70697145</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1372479035996504</v>
+        <v>0.1404747174175633</v>
       </c>
       <c r="T75">
-        <v>1.782489853050647</v>
+        <v>1.845386460427169</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.334910337657242</v>
+        <v>3.289843981742955</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7590,22 +7590,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07209892652856646</v>
+        <v>0.0720461690852273</v>
       </c>
       <c r="C76">
-        <v>248.5287267968395</v>
+        <v>243.5308433847422</v>
       </c>
       <c r="D76">
-        <v>707.9827267968394</v>
+        <v>709.4058433847422</v>
       </c>
       <c r="E76">
-        <v>444.554</v>
+        <v>450.975</v>
       </c>
       <c r="F76">
-        <v>475.154</v>
+        <v>481.575</v>
       </c>
       <c r="G76">
         <v>15.7</v>
@@ -7626,28 +7626,28 @@
         <v>100.2</v>
       </c>
       <c r="M76">
-        <v>30.4573714</v>
+        <v>30.8689575</v>
       </c>
       <c r="N76">
-        <v>69.7426286</v>
+        <v>69.3310425</v>
       </c>
       <c r="O76">
-        <v>17.43565715</v>
+        <v>17.332760625</v>
       </c>
       <c r="P76">
-        <v>52.30697145000001</v>
+        <v>51.998281875</v>
       </c>
       <c r="Q76">
-        <v>109.70697145</v>
+        <v>109.398281875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1404747174175633</v>
+        <v>0.1439596763409092</v>
       </c>
       <c r="T76">
-        <v>1.845386460427169</v>
+        <v>1.913314796393814</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.289843981742955</v>
+        <v>3.245979395319715</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7672,22 +7672,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0720461690852273</v>
+        <v>0.07199341164188813</v>
       </c>
       <c r="C77">
-        <v>243.5308433847422</v>
+        <v>238.5386927113796</v>
       </c>
       <c r="D77">
-        <v>709.4058433847422</v>
+        <v>710.8346927113796</v>
       </c>
       <c r="E77">
-        <v>450.975</v>
+        <v>457.396</v>
       </c>
       <c r="F77">
-        <v>481.575</v>
+        <v>487.996</v>
       </c>
       <c r="G77">
         <v>15.7</v>
@@ -7708,28 +7708,28 @@
         <v>100.2</v>
       </c>
       <c r="M77">
-        <v>30.8689575</v>
+        <v>31.28054360000001</v>
       </c>
       <c r="N77">
-        <v>69.3310425</v>
+        <v>68.9194564</v>
       </c>
       <c r="O77">
-        <v>17.332760625</v>
+        <v>17.2298641</v>
       </c>
       <c r="P77">
-        <v>51.998281875</v>
+        <v>51.6895923</v>
       </c>
       <c r="Q77">
-        <v>109.398281875</v>
+        <v>109.0895923</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1439596763409092</v>
+        <v>0.1477350485078672</v>
       </c>
       <c r="T77">
-        <v>1.913314796393814</v>
+        <v>1.986903827024345</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.245979395319715</v>
+        <v>3.20326914011814</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7754,22 +7754,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07199341164188813</v>
+        <v>0.07194065419854898</v>
       </c>
       <c r="C78">
-        <v>238.5386927113796</v>
+        <v>233.5523094864376</v>
       </c>
       <c r="D78">
-        <v>710.8346927113796</v>
+        <v>712.2693094864376</v>
       </c>
       <c r="E78">
-        <v>457.396</v>
+        <v>463.817</v>
       </c>
       <c r="F78">
-        <v>487.996</v>
+        <v>494.417</v>
       </c>
       <c r="G78">
         <v>15.7</v>
@@ -7790,28 +7790,28 @@
         <v>100.2</v>
       </c>
       <c r="M78">
-        <v>31.28054360000001</v>
+        <v>31.6921297</v>
       </c>
       <c r="N78">
-        <v>68.9194564</v>
+        <v>68.50787030000001</v>
       </c>
       <c r="O78">
-        <v>17.2298641</v>
+        <v>17.126967575</v>
       </c>
       <c r="P78">
-        <v>51.6895923</v>
+        <v>51.38090272500001</v>
       </c>
       <c r="Q78">
-        <v>109.0895923</v>
+        <v>108.780902725</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1477350485078672</v>
+        <v>0.1518387139067347</v>
       </c>
       <c r="T78">
-        <v>1.986903827024345</v>
+        <v>2.066891903796662</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.20326914011814</v>
+        <v>3.161668242194528</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7836,22 +7836,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07194065419854898</v>
+        <v>0.07188789675520982</v>
       </c>
       <c r="C79">
-        <v>233.5523094864376</v>
+        <v>228.5717287003761</v>
       </c>
       <c r="D79">
-        <v>712.2693094864376</v>
+        <v>713.7097287003761</v>
       </c>
       <c r="E79">
-        <v>463.817</v>
+        <v>470.238</v>
       </c>
       <c r="F79">
-        <v>494.417</v>
+        <v>500.838</v>
       </c>
       <c r="G79">
         <v>15.7</v>
@@ -7872,28 +7872,28 @@
         <v>100.2</v>
       </c>
       <c r="M79">
-        <v>31.6921297</v>
+        <v>32.1037158</v>
       </c>
       <c r="N79">
-        <v>68.50787030000001</v>
+        <v>68.0962842</v>
       </c>
       <c r="O79">
-        <v>17.126967575</v>
+        <v>17.02407105</v>
       </c>
       <c r="P79">
-        <v>51.38090272500001</v>
+        <v>51.07221315</v>
       </c>
       <c r="Q79">
-        <v>108.780902725</v>
+        <v>108.47221315</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1518387139067347</v>
+        <v>0.1563154397964082</v>
       </c>
       <c r="T79">
-        <v>2.066891903796662</v>
+        <v>2.154151623911916</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.161668242194528</v>
+        <v>3.121134033961265</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7918,22 +7918,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07188789675520982</v>
+        <v>0.07183513931187066</v>
       </c>
       <c r="C80">
-        <v>228.5717287003761</v>
+        <v>223.5969856272729</v>
       </c>
       <c r="D80">
-        <v>713.7097287003761</v>
+        <v>715.1559856272729</v>
       </c>
       <c r="E80">
-        <v>470.238</v>
+        <v>476.659</v>
       </c>
       <c r="F80">
-        <v>500.838</v>
+        <v>507.259</v>
       </c>
       <c r="G80">
         <v>15.7</v>
@@ -7954,28 +7954,28 @@
         <v>100.2</v>
       </c>
       <c r="M80">
-        <v>32.1037158</v>
+        <v>32.5153019</v>
       </c>
       <c r="N80">
-        <v>68.0962842</v>
+        <v>67.68469809999999</v>
       </c>
       <c r="O80">
-        <v>17.02407105</v>
+        <v>16.921174525</v>
       </c>
       <c r="P80">
-        <v>51.07221315</v>
+        <v>50.76352357499999</v>
       </c>
       <c r="Q80">
-        <v>108.47221315</v>
+        <v>108.163523575</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1563154397964082</v>
+        <v>0.1612185205327174</v>
       </c>
       <c r="T80">
-        <v>2.154151623911916</v>
+        <v>2.249721793561957</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.121134033961265</v>
+        <v>3.081626008214919</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8000,22 +8000,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07183513931187066</v>
+        <v>0.0717823818685315</v>
       </c>
       <c r="C81">
-        <v>223.5969856272729</v>
+        <v>218.6281158277026</v>
       </c>
       <c r="D81">
-        <v>715.1559856272729</v>
+        <v>716.6081158277026</v>
       </c>
       <c r="E81">
-        <v>476.659</v>
+        <v>483.08</v>
       </c>
       <c r="F81">
-        <v>507.259</v>
+        <v>513.6800000000001</v>
       </c>
       <c r="G81">
         <v>15.7</v>
@@ -8036,28 +8036,28 @@
         <v>100.2</v>
       </c>
       <c r="M81">
-        <v>32.5153019</v>
+        <v>32.92688800000001</v>
       </c>
       <c r="N81">
-        <v>67.68469809999999</v>
+        <v>67.273112</v>
       </c>
       <c r="O81">
-        <v>16.921174525</v>
+        <v>16.818278</v>
       </c>
       <c r="P81">
-        <v>50.76352357499999</v>
+        <v>50.454834</v>
       </c>
       <c r="Q81">
-        <v>108.163523575</v>
+        <v>107.854834</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1612185205327174</v>
+        <v>0.1666119093426575</v>
       </c>
       <c r="T81">
-        <v>2.249721793561957</v>
+        <v>2.354848980177002</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.081626008214919</v>
+        <v>3.043105683112233</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8082,22 +8082,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0717823818685315</v>
+        <v>0.07172962442519235</v>
       </c>
       <c r="C82">
-        <v>218.6281158277026</v>
+        <v>213.6651551516517</v>
       </c>
       <c r="D82">
-        <v>716.6081158277026</v>
+        <v>718.0661551516516</v>
       </c>
       <c r="E82">
-        <v>483.08</v>
+        <v>489.501</v>
       </c>
       <c r="F82">
-        <v>513.6800000000001</v>
+        <v>520.101</v>
       </c>
       <c r="G82">
         <v>15.7</v>
@@ -8118,28 +8118,28 @@
         <v>100.2</v>
       </c>
       <c r="M82">
-        <v>32.92688800000001</v>
+        <v>33.3384741</v>
       </c>
       <c r="N82">
-        <v>67.273112</v>
+        <v>66.8615259</v>
       </c>
       <c r="O82">
-        <v>16.818278</v>
+        <v>16.715381475</v>
       </c>
       <c r="P82">
-        <v>50.454834</v>
+        <v>50.146144425</v>
       </c>
       <c r="Q82">
-        <v>107.854834</v>
+        <v>107.546144425</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1666119093426575</v>
+        <v>0.172573023290486</v>
       </c>
       <c r="T82">
-        <v>2.354848980177002</v>
+        <v>2.471042186435736</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.043105683112233</v>
+        <v>3.005536477147885</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8164,22 +8164,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07172962442519235</v>
+        <v>0.07647386698185317</v>
       </c>
       <c r="C83">
-        <v>213.6651551516517</v>
+        <v>96.18283987035079</v>
       </c>
       <c r="D83">
-        <v>718.0661551516516</v>
+        <v>607.0048398703508</v>
       </c>
       <c r="E83">
-        <v>489.501</v>
+        <v>495.922</v>
       </c>
       <c r="F83">
-        <v>520.101</v>
+        <v>526.522</v>
       </c>
       <c r="G83">
         <v>15.7</v>
@@ -8200,45 +8200,45 @@
         <v>100.2</v>
       </c>
       <c r="M83">
-        <v>33.3384741</v>
+        <v>37.85693180000001</v>
       </c>
       <c r="N83">
-        <v>66.8615259</v>
+        <v>62.3430682</v>
       </c>
       <c r="O83">
-        <v>16.715381475</v>
+        <v>15.58576705</v>
       </c>
       <c r="P83">
-        <v>50.146144425</v>
+        <v>46.75730115</v>
       </c>
       <c r="Q83">
-        <v>107.546144425</v>
+        <v>104.15730115</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.172573023290486</v>
+        <v>0.1791964832325177</v>
       </c>
       <c r="T83">
-        <v>2.471042186435736</v>
+        <v>2.60014574894544</v>
       </c>
       <c r="U83">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V83">
         <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.005536477147885</v>
+        <v>2.646807209030078</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8246,22 +8246,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07647386698185317</v>
+        <v>0.07647960953851402</v>
       </c>
       <c r="C84">
-        <v>96.18283987035079</v>
+        <v>89.64822174617007</v>
       </c>
       <c r="D84">
-        <v>607.0048398703508</v>
+        <v>606.8912217461701</v>
       </c>
       <c r="E84">
-        <v>495.922</v>
+        <v>502.3430000000001</v>
       </c>
       <c r="F84">
-        <v>526.522</v>
+        <v>532.9430000000001</v>
       </c>
       <c r="G84">
         <v>15.7</v>
@@ -8282,28 +8282,28 @@
         <v>100.2</v>
       </c>
       <c r="M84">
-        <v>37.85693180000001</v>
+        <v>38.31860170000001</v>
       </c>
       <c r="N84">
-        <v>62.3430682</v>
+        <v>61.88139829999999</v>
       </c>
       <c r="O84">
-        <v>15.58576705</v>
+        <v>15.470349575</v>
       </c>
       <c r="P84">
-        <v>46.75730115</v>
+        <v>46.41104872499999</v>
       </c>
       <c r="Q84">
-        <v>104.15730115</v>
+        <v>103.811048725</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1791964832325177</v>
+        <v>0.1865991737559648</v>
       </c>
       <c r="T84">
-        <v>2.60014574894544</v>
+        <v>2.74443796586805</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.646807209030078</v>
+        <v>2.614917965547787</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8328,22 +8328,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07647960953851402</v>
+        <v>0.07648535209517485</v>
       </c>
       <c r="C85">
-        <v>89.64822174617007</v>
+        <v>83.11364614772071</v>
       </c>
       <c r="D85">
-        <v>606.8912217461701</v>
+        <v>606.7776461477207</v>
       </c>
       <c r="E85">
-        <v>502.3430000000001</v>
+        <v>508.764</v>
       </c>
       <c r="F85">
-        <v>532.9430000000001</v>
+        <v>539.364</v>
       </c>
       <c r="G85">
         <v>15.7</v>
@@ -8364,28 +8364,28 @@
         <v>100.2</v>
       </c>
       <c r="M85">
-        <v>38.31860170000001</v>
+        <v>38.78027160000001</v>
       </c>
       <c r="N85">
-        <v>61.88139829999999</v>
+        <v>61.4197284</v>
       </c>
       <c r="O85">
-        <v>15.470349575</v>
+        <v>15.3549321</v>
       </c>
       <c r="P85">
-        <v>46.41104872499999</v>
+        <v>46.0647963</v>
       </c>
       <c r="Q85">
-        <v>103.811048725</v>
+        <v>103.4647963</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1865991737559648</v>
+        <v>0.1949272005948429</v>
       </c>
       <c r="T85">
-        <v>2.74443796586805</v>
+        <v>2.906766709905988</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.614917965547787</v>
+        <v>2.583787989767456</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8410,22 +8410,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07648535209517485</v>
+        <v>0.07649109465183569</v>
       </c>
       <c r="C86">
-        <v>83.11364614772071</v>
+        <v>76.57911305113157</v>
       </c>
       <c r="D86">
-        <v>606.7776461477207</v>
+        <v>606.6641130511315</v>
       </c>
       <c r="E86">
-        <v>508.764</v>
+        <v>515.1849999999999</v>
       </c>
       <c r="F86">
-        <v>539.364</v>
+        <v>545.785</v>
       </c>
       <c r="G86">
         <v>15.7</v>
@@ -8446,28 +8446,28 @@
         <v>100.2</v>
       </c>
       <c r="M86">
-        <v>38.78027160000001</v>
+        <v>39.2419415</v>
       </c>
       <c r="N86">
-        <v>61.4197284</v>
+        <v>60.9580585</v>
       </c>
       <c r="O86">
-        <v>15.3549321</v>
+        <v>15.239514625</v>
       </c>
       <c r="P86">
-        <v>46.0647963</v>
+        <v>45.718543875</v>
       </c>
       <c r="Q86">
-        <v>103.4647963</v>
+        <v>103.118543875</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1949272005948428</v>
+        <v>0.2043656310122379</v>
       </c>
       <c r="T86">
-        <v>2.906766709905986</v>
+        <v>3.090739286482314</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.583787989767456</v>
+        <v>2.553390484005487</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8492,22 +8492,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07649109465183569</v>
+        <v>0.07649683720849652</v>
       </c>
       <c r="C87">
-        <v>76.57911305113157</v>
+        <v>70.04462243254989</v>
       </c>
       <c r="D87">
-        <v>606.6641130511315</v>
+        <v>606.5506224325499</v>
       </c>
       <c r="E87">
-        <v>515.1849999999999</v>
+        <v>521.606</v>
       </c>
       <c r="F87">
-        <v>545.785</v>
+        <v>552.206</v>
       </c>
       <c r="G87">
         <v>15.7</v>
@@ -8528,28 +8528,28 @@
         <v>100.2</v>
       </c>
       <c r="M87">
-        <v>39.2419415</v>
+        <v>39.70361140000001</v>
       </c>
       <c r="N87">
-        <v>60.9580585</v>
+        <v>60.4963886</v>
       </c>
       <c r="O87">
-        <v>15.239514625</v>
+        <v>15.12409715</v>
       </c>
       <c r="P87">
-        <v>45.718543875</v>
+        <v>45.37229145</v>
       </c>
       <c r="Q87">
-        <v>103.118543875</v>
+        <v>102.77229145</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2043656310122379</v>
+        <v>0.215152408632118</v>
       </c>
       <c r="T87">
-        <v>3.090739286482314</v>
+        <v>3.300993659712403</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.553390484005487</v>
+        <v>2.523699896982167</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8574,22 +8574,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07649683720849652</v>
+        <v>0.07904732976515737</v>
       </c>
       <c r="C88">
-        <v>70.04462243254989</v>
+        <v>17.09348426267331</v>
       </c>
       <c r="D88">
-        <v>606.5506224325499</v>
+        <v>560.0204842626733</v>
       </c>
       <c r="E88">
-        <v>521.606</v>
+        <v>528.027</v>
       </c>
       <c r="F88">
-        <v>552.206</v>
+        <v>558.6270000000001</v>
       </c>
       <c r="G88">
         <v>15.7</v>
@@ -8610,45 +8610,45 @@
         <v>100.2</v>
       </c>
       <c r="M88">
-        <v>39.70361140000001</v>
+        <v>42.34392660000001</v>
       </c>
       <c r="N88">
-        <v>60.4963886</v>
+        <v>57.85607339999999</v>
       </c>
       <c r="O88">
-        <v>15.12409715</v>
+        <v>14.46401835</v>
       </c>
       <c r="P88">
-        <v>45.37229145</v>
+        <v>43.39205505</v>
       </c>
       <c r="Q88">
-        <v>102.77229145</v>
+        <v>100.79205505</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.215152408632118</v>
+        <v>0.2275986905012105</v>
       </c>
       <c r="T88">
-        <v>3.300993659712403</v>
+        <v>3.543594859593275</v>
       </c>
       <c r="U88">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V88">
         <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.523699896982167</v>
+        <v>2.366336994358949</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8656,22 +8656,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07904732976515737</v>
+        <v>0.07908232232181821</v>
       </c>
       <c r="C89">
-        <v>17.09348426267331</v>
+        <v>10.08368675217196</v>
       </c>
       <c r="D89">
-        <v>560.0204842626733</v>
+        <v>559.4316867521719</v>
       </c>
       <c r="E89">
-        <v>528.027</v>
+        <v>534.448</v>
       </c>
       <c r="F89">
-        <v>558.6270000000001</v>
+        <v>565.048</v>
       </c>
       <c r="G89">
         <v>15.7</v>
@@ -8692,28 +8692,28 @@
         <v>100.2</v>
       </c>
       <c r="M89">
-        <v>42.34392660000001</v>
+        <v>42.83063840000001</v>
       </c>
       <c r="N89">
-        <v>57.85607339999999</v>
+        <v>57.3693616</v>
       </c>
       <c r="O89">
-        <v>14.46401835</v>
+        <v>14.3423404</v>
       </c>
       <c r="P89">
-        <v>43.39205505</v>
+        <v>43.0270212</v>
       </c>
       <c r="Q89">
-        <v>100.79205505</v>
+        <v>100.4270212</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2275986905012105</v>
+        <v>0.2421193526818184</v>
       </c>
       <c r="T89">
-        <v>3.543594859593275</v>
+        <v>3.826629592787627</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8730,7 +8730,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.366336994358949</v>
+        <v>2.339446801241235</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8738,22 +8738,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07908232232181821</v>
+        <v>0.07911731487847905</v>
       </c>
       <c r="C90">
-        <v>10.08368675217196</v>
+        <v>3.075126047837102</v>
       </c>
       <c r="D90">
-        <v>559.4316867521719</v>
+        <v>558.8441260478371</v>
       </c>
       <c r="E90">
-        <v>534.448</v>
+        <v>540.869</v>
       </c>
       <c r="F90">
-        <v>565.048</v>
+        <v>571.4690000000001</v>
       </c>
       <c r="G90">
         <v>15.7</v>
@@ -8774,28 +8774,28 @@
         <v>100.2</v>
       </c>
       <c r="M90">
-        <v>42.83063840000001</v>
+        <v>43.31735020000001</v>
       </c>
       <c r="N90">
-        <v>57.3693616</v>
+        <v>56.8826498</v>
       </c>
       <c r="O90">
-        <v>14.3423404</v>
+        <v>14.22066245</v>
       </c>
       <c r="P90">
-        <v>43.0270212</v>
+        <v>42.66198735</v>
       </c>
       <c r="Q90">
-        <v>100.4270212</v>
+        <v>100.06198735</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2421193526818184</v>
+        <v>0.2592801352589004</v>
       </c>
       <c r="T90">
-        <v>3.826629592787627</v>
+        <v>4.16112518656277</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.339446801241235</v>
+        <v>2.313160882126164</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8820,22 +8820,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07911731487847905</v>
+        <v>0.07915230743513987</v>
       </c>
       <c r="C91">
-        <v>3.075126047837102</v>
+        <v>-3.932201743225846</v>
       </c>
       <c r="D91">
-        <v>558.8441260478371</v>
+        <v>558.2577982567741</v>
       </c>
       <c r="E91">
-        <v>540.869</v>
+        <v>547.29</v>
       </c>
       <c r="F91">
-        <v>571.4690000000001</v>
+        <v>577.89</v>
       </c>
       <c r="G91">
         <v>15.7</v>
@@ -8856,28 +8856,28 @@
         <v>100.2</v>
       </c>
       <c r="M91">
-        <v>43.31735020000001</v>
+        <v>43.804062</v>
       </c>
       <c r="N91">
-        <v>56.8826498</v>
+        <v>56.395938</v>
       </c>
       <c r="O91">
-        <v>14.22066245</v>
+        <v>14.0989845</v>
       </c>
       <c r="P91">
-        <v>42.66198735</v>
+        <v>42.2969535</v>
       </c>
       <c r="Q91">
-        <v>100.06198735</v>
+        <v>99.69695349999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2592801352589004</v>
+        <v>0.2798730743513989</v>
       </c>
       <c r="T91">
-        <v>4.16112518656277</v>
+        <v>4.562519899092941</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.313160882126164</v>
+        <v>2.287459094546985</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8902,22 +8902,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07915230743513987</v>
+        <v>0.07918729999180073</v>
       </c>
       <c r="C92">
-        <v>-3.932201743225846</v>
+        <v>-10.93830049759231</v>
       </c>
       <c r="D92">
-        <v>558.2577982567741</v>
+        <v>557.6726995024077</v>
       </c>
       <c r="E92">
-        <v>547.29</v>
+        <v>553.711</v>
       </c>
       <c r="F92">
-        <v>577.89</v>
+        <v>584.311</v>
       </c>
       <c r="G92">
         <v>15.7</v>
@@ -8938,28 +8938,28 @@
         <v>100.2</v>
       </c>
       <c r="M92">
-        <v>43.804062</v>
+        <v>44.2907738</v>
       </c>
       <c r="N92">
-        <v>56.395938</v>
+        <v>55.9092262</v>
       </c>
       <c r="O92">
-        <v>14.0989845</v>
+        <v>13.97730655</v>
       </c>
       <c r="P92">
-        <v>42.2969535</v>
+        <v>41.93191965</v>
       </c>
       <c r="Q92">
-        <v>99.69695349999999</v>
+        <v>99.33191964999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2798730743513989</v>
+        <v>0.3050422221311192</v>
       </c>
       <c r="T92">
-        <v>4.562519899092941</v>
+        <v>5.053113436629816</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8976,7 +8976,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.287459094546985</v>
+        <v>2.262322181420095</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8984,22 +8984,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07918729999180073</v>
+        <v>0.07922229254846157</v>
       </c>
       <c r="C93">
-        <v>-10.93830049759231</v>
+        <v>-17.94317407560163</v>
       </c>
       <c r="D93">
-        <v>557.6726995024077</v>
+        <v>557.0888259243984</v>
       </c>
       <c r="E93">
-        <v>553.711</v>
+        <v>560.1320000000001</v>
       </c>
       <c r="F93">
-        <v>584.311</v>
+        <v>590.7320000000001</v>
       </c>
       <c r="G93">
         <v>15.7</v>
@@ -9020,28 +9020,28 @@
         <v>100.2</v>
       </c>
       <c r="M93">
-        <v>44.2907738</v>
+        <v>44.77748560000001</v>
       </c>
       <c r="N93">
-        <v>55.9092262</v>
+        <v>55.42251439999999</v>
       </c>
       <c r="O93">
-        <v>13.97730655</v>
+        <v>13.8556286</v>
       </c>
       <c r="P93">
-        <v>41.93191965</v>
+        <v>41.56688579999999</v>
       </c>
       <c r="Q93">
-        <v>99.33191964999999</v>
+        <v>98.96688579999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3050422221311192</v>
+        <v>0.3365036568557697</v>
       </c>
       <c r="T93">
-        <v>5.053113436629816</v>
+        <v>5.666355358550913</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.262322181420095</v>
+        <v>2.237731722926398</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9066,22 +9066,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07922229254846157</v>
+        <v>0.07925728510512241</v>
       </c>
       <c r="C94">
-        <v>-17.94317407560163</v>
+        <v>-24.94682632144372</v>
       </c>
       <c r="D94">
-        <v>557.0888259243984</v>
+        <v>556.5061736785563</v>
       </c>
       <c r="E94">
-        <v>560.1320000000001</v>
+        <v>566.553</v>
       </c>
       <c r="F94">
-        <v>590.7320000000001</v>
+        <v>597.153</v>
       </c>
       <c r="G94">
         <v>15.7</v>
@@ -9102,28 +9102,28 @@
         <v>100.2</v>
       </c>
       <c r="M94">
-        <v>44.77748560000001</v>
+        <v>45.26419740000001</v>
       </c>
       <c r="N94">
-        <v>55.42251439999999</v>
+        <v>54.9358026</v>
       </c>
       <c r="O94">
-        <v>13.8556286</v>
+        <v>13.73395065</v>
       </c>
       <c r="P94">
-        <v>41.56688579999999</v>
+        <v>41.20185195</v>
       </c>
       <c r="Q94">
-        <v>98.96688579999999</v>
+        <v>98.60185195</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3365036568557697</v>
+        <v>0.3769540729303202</v>
       </c>
       <c r="T94">
-        <v>5.666355358550913</v>
+        <v>6.45480925816375</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.237731722926398</v>
+        <v>2.213670091497082</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9148,22 +9148,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07925728510512241</v>
+        <v>0.07929227766178323</v>
       </c>
       <c r="C95">
-        <v>-24.94682632144372</v>
+        <v>-31.94926106324294</v>
       </c>
       <c r="D95">
-        <v>556.5061736785563</v>
+        <v>555.9247389367571</v>
       </c>
       <c r="E95">
-        <v>566.553</v>
+        <v>572.974</v>
       </c>
       <c r="F95">
-        <v>597.153</v>
+        <v>603.5740000000001</v>
       </c>
       <c r="G95">
         <v>15.7</v>
@@ -9184,28 +9184,28 @@
         <v>100.2</v>
       </c>
       <c r="M95">
-        <v>45.26419740000001</v>
+        <v>45.75090920000001</v>
       </c>
       <c r="N95">
-        <v>54.9358026</v>
+        <v>54.44909079999999</v>
       </c>
       <c r="O95">
-        <v>13.73395065</v>
+        <v>13.6122727</v>
       </c>
       <c r="P95">
-        <v>41.20185195</v>
+        <v>40.8368181</v>
       </c>
       <c r="Q95">
-        <v>98.60185195</v>
+        <v>98.23681809999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3769540729303202</v>
+        <v>0.4308879610297209</v>
       </c>
       <c r="T95">
-        <v>6.45480925816375</v>
+        <v>7.506081124314198</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9222,7 +9222,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.213670091497082</v>
+        <v>2.190120409672645</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9230,22 +9230,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07929227766178323</v>
+        <v>0.07932727021844409</v>
       </c>
       <c r="C96">
-        <v>-31.94926106324294</v>
+        <v>-38.9504821131427</v>
       </c>
       <c r="D96">
-        <v>555.9247389367571</v>
+        <v>555.3445178868574</v>
       </c>
       <c r="E96">
-        <v>572.974</v>
+        <v>579.3950000000001</v>
       </c>
       <c r="F96">
-        <v>603.5740000000001</v>
+        <v>609.9950000000001</v>
       </c>
       <c r="G96">
         <v>15.7</v>
@@ -9266,28 +9266,28 @@
         <v>100.2</v>
       </c>
       <c r="M96">
-        <v>45.75090920000001</v>
+        <v>46.23762100000001</v>
       </c>
       <c r="N96">
-        <v>54.44909079999999</v>
+        <v>53.96237899999999</v>
       </c>
       <c r="O96">
-        <v>13.6122727</v>
+        <v>13.49059475</v>
       </c>
       <c r="P96">
-        <v>40.8368181</v>
+        <v>40.47178424999999</v>
       </c>
       <c r="Q96">
-        <v>98.23681809999999</v>
+        <v>97.87178424999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4308879610297209</v>
+        <v>0.5063954043688822</v>
       </c>
       <c r="T96">
-        <v>7.506081124314198</v>
+        <v>8.977861736924831</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.190120409672645</v>
+        <v>2.167066510623459</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9312,22 +9312,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07932727021844409</v>
+        <v>0.07936226277510491</v>
       </c>
       <c r="C97">
-        <v>-38.9504821131427</v>
+        <v>-45.95049326738615</v>
       </c>
       <c r="D97">
-        <v>555.3445178868574</v>
+        <v>554.7655067326139</v>
       </c>
       <c r="E97">
-        <v>579.3950000000001</v>
+        <v>585.816</v>
       </c>
       <c r="F97">
-        <v>609.9950000000001</v>
+        <v>616.4160000000001</v>
       </c>
       <c r="G97">
         <v>15.7</v>
@@ -9348,28 +9348,28 @@
         <v>100.2</v>
       </c>
       <c r="M97">
-        <v>46.23762100000001</v>
+        <v>46.72433280000001</v>
       </c>
       <c r="N97">
-        <v>53.96237899999999</v>
+        <v>53.4756672</v>
       </c>
       <c r="O97">
-        <v>13.49059475</v>
+        <v>13.3689168</v>
       </c>
       <c r="P97">
-        <v>40.47178424999999</v>
+        <v>40.1067504</v>
       </c>
       <c r="Q97">
-        <v>97.87178424999999</v>
+        <v>97.50675039999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5063954043688822</v>
+        <v>0.6196565693776239</v>
       </c>
       <c r="T97">
-        <v>8.977861736924831</v>
+        <v>11.18553265584078</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.167066510623459</v>
+        <v>2.144492901137799</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9394,22 +9394,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07936226277510491</v>
+        <v>0.07939725533176575</v>
       </c>
       <c r="C98">
-        <v>-45.95049326738615</v>
+        <v>-52.94929830640262</v>
       </c>
       <c r="D98">
-        <v>554.7655067326139</v>
+        <v>554.1877016935973</v>
       </c>
       <c r="E98">
-        <v>585.816</v>
+        <v>592.237</v>
       </c>
       <c r="F98">
-        <v>616.4160000000001</v>
+        <v>622.837</v>
       </c>
       <c r="G98">
         <v>15.7</v>
@@ -9430,28 +9430,28 @@
         <v>100.2</v>
       </c>
       <c r="M98">
-        <v>46.72433280000001</v>
+        <v>47.2110446</v>
       </c>
       <c r="N98">
-        <v>53.4756672</v>
+        <v>52.9889554</v>
       </c>
       <c r="O98">
-        <v>13.3689168</v>
+        <v>13.24723885</v>
       </c>
       <c r="P98">
-        <v>40.1067504</v>
+        <v>39.74171655</v>
       </c>
       <c r="Q98">
-        <v>97.50675039999999</v>
+        <v>97.14171654999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6196565693776225</v>
+        <v>0.8084251777255245</v>
       </c>
       <c r="T98">
-        <v>11.18553265584075</v>
+        <v>14.86498418736731</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.144492901137799</v>
+        <v>2.122384726899265</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9476,22 +9476,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07939725533176575</v>
+        <v>0.07943224788842661</v>
       </c>
       <c r="C99">
-        <v>-52.94929830640262</v>
+        <v>-59.94690099488764</v>
       </c>
       <c r="D99">
-        <v>554.1877016935973</v>
+        <v>553.6110990051124</v>
       </c>
       <c r="E99">
-        <v>592.237</v>
+        <v>598.658</v>
       </c>
       <c r="F99">
-        <v>622.837</v>
+        <v>629.258</v>
       </c>
       <c r="G99">
         <v>15.7</v>
@@ -9512,28 +9512,28 @@
         <v>100.2</v>
       </c>
       <c r="M99">
-        <v>47.2110446</v>
+        <v>47.69775640000001</v>
       </c>
       <c r="N99">
-        <v>52.9889554</v>
+        <v>52.50224359999999</v>
       </c>
       <c r="O99">
-        <v>13.24723885</v>
+        <v>13.1255609</v>
       </c>
       <c r="P99">
-        <v>39.74171655</v>
+        <v>39.3766827</v>
       </c>
       <c r="Q99">
-        <v>97.14171654999998</v>
+        <v>96.77668269999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8084251777255245</v>
+        <v>1.185962394421329</v>
       </c>
       <c r="T99">
-        <v>14.86498418736731</v>
+        <v>22.22388725042043</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.122384726899265</v>
+        <v>2.100727739890088</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9558,22 +9558,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07943224788842661</v>
+        <v>0.07946724044508743</v>
       </c>
       <c r="C100">
-        <v>-59.94690099488764</v>
+        <v>-66.94330508188409</v>
       </c>
       <c r="D100">
-        <v>553.6110990051124</v>
+        <v>553.0356949181158</v>
       </c>
       <c r="E100">
-        <v>598.658</v>
+        <v>605.079</v>
       </c>
       <c r="F100">
-        <v>629.258</v>
+        <v>635.679</v>
       </c>
       <c r="G100">
         <v>15.7</v>
@@ -9594,28 +9594,28 @@
         <v>100.2</v>
       </c>
       <c r="M100">
-        <v>47.69775640000001</v>
+        <v>48.1844682</v>
       </c>
       <c r="N100">
-        <v>52.50224359999999</v>
+        <v>52.0155318</v>
       </c>
       <c r="O100">
-        <v>13.1255609</v>
+        <v>13.00388295</v>
       </c>
       <c r="P100">
-        <v>39.3766827</v>
+        <v>39.01164885</v>
       </c>
       <c r="Q100">
-        <v>96.77668269999998</v>
+        <v>96.41164884999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.185962394421329</v>
+        <v>2.318574044508741</v>
       </c>
       <c r="T100">
-        <v>22.22388725042043</v>
+        <v>44.30059643957981</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9632,91 +9632,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.100727739890088</v>
+        <v>2.079508267769986</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07946724044508743</v>
-      </c>
-      <c r="C101">
-        <v>-66.94330508188409</v>
-      </c>
-      <c r="D101">
-        <v>553.0356949181158</v>
-      </c>
-      <c r="E101">
-        <v>605.079</v>
-      </c>
-      <c r="F101">
-        <v>635.679</v>
-      </c>
-      <c r="G101">
-        <v>15.7</v>
-      </c>
-      <c r="H101">
-        <v>611.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>157.6</v>
-      </c>
-      <c r="K101">
-        <v>57.39999999999999</v>
-      </c>
-      <c r="L101">
-        <v>100.2</v>
-      </c>
-      <c r="M101">
-        <v>48.1844682</v>
-      </c>
-      <c r="N101">
-        <v>52.0155318</v>
-      </c>
-      <c r="O101">
-        <v>13.00388295</v>
-      </c>
-      <c r="P101">
-        <v>39.01164885</v>
-      </c>
-      <c r="Q101">
-        <v>96.41164884999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.318574044508741</v>
-      </c>
-      <c r="T101">
-        <v>44.30059643957981</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.079508267769986</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
